--- a/data/vignesh_jobs.xlsx
+++ b/data/vignesh_jobs.xlsx
@@ -536,7 +536,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-09-03 05:10:31</t>
+          <t>2026-09-03 07:13:21</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -607,7 +607,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-09-03 05:10:31</t>
+          <t>2026-09-03 07:13:21</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-09-03 05:10:31</t>
+          <t>2026-09-03 07:13:21</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -749,7 +749,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-09-03 05:10:31</t>
+          <t>2026-09-03 07:13:21</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">

--- a/data/vignesh_jobs.xlsx
+++ b/data/vignesh_jobs.xlsx
@@ -536,7 +536,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-09-03 07:13:21</t>
+          <t>2026-09-03 07:33:38</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -607,7 +607,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-09-03 07:13:21</t>
+          <t>2026-09-03 07:33:38</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-09-03 07:13:21</t>
+          <t>2026-09-03 07:33:38</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -749,7 +749,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-09-03 07:13:21</t>
+          <t>2026-09-03 07:33:38</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">

--- a/data/vignesh_jobs.xlsx
+++ b/data/vignesh_jobs.xlsx
@@ -536,7 +536,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-09-03 07:33:38</t>
+          <t>2026-09-03 08:50:20</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -607,7 +607,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-09-03 07:33:38</t>
+          <t>2026-09-03 08:50:20</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-09-03 07:33:38</t>
+          <t>2026-09-03 08:50:20</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -749,7 +749,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-09-03 07:33:38</t>
+          <t>2026-09-03 08:50:20</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">

--- a/data/vignesh_jobs.xlsx
+++ b/data/vignesh_jobs.xlsx
@@ -536,7 +536,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-09-03 08:50:20</t>
+          <t>2026-09-03 09:26:35</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -545,11 +545,11 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>skill:Python, skill:Bash</t>
+          <t>skill:Python, skill:Bash, skill:Kubernetes</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -607,7 +607,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-09-03 08:50:20</t>
+          <t>2026-09-03 09:26:35</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-09-03 08:50:20</t>
+          <t>2026-09-03 09:26:35</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -749,7 +749,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-09-03 08:50:20</t>
+          <t>2026-09-03 09:26:35</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">

--- a/data/vignesh_jobs.xlsx
+++ b/data/vignesh_jobs.xlsx
@@ -536,7 +536,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-09-03 09:26:35</t>
+          <t>2026-09-03 09:46:04</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -607,7 +607,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-09-03 09:26:35</t>
+          <t>2026-09-03 09:46:04</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-09-03 09:26:35</t>
+          <t>2026-09-03 09:46:04</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -749,7 +749,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-09-03 09:26:35</t>
+          <t>2026-09-03 09:46:04</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">

--- a/data/vignesh_jobs.xlsx
+++ b/data/vignesh_jobs.xlsx
@@ -536,7 +536,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-09-03 09:46:04</t>
+          <t>2026-09-03 09:50:48</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -607,7 +607,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-09-03 09:46:04</t>
+          <t>2026-09-03 09:50:48</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-09-03 09:46:04</t>
+          <t>2026-09-03 09:50:48</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -749,7 +749,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-09-03 09:46:04</t>
+          <t>2026-09-03 09:50:48</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">

--- a/data/vignesh_jobs.xlsx
+++ b/data/vignesh_jobs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O5"/>
+  <dimension ref="A1:O48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -496,17 +496,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0fa3d588c2f7472524a1</t>
+          <t>b2e4b2d2bb50978abe16</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Tekskills India Private Limited</t>
+          <t>Moody's</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Staff Software Engineer</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -516,12 +516,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>We are hiring an experienced Platform Engineer with strong expertise in Cloudera, Kafka, Databricks, Azure Synapse, PySpark, and Infrastructure Automation . Mandatory Skills Cloudera Platform Administration Cloudera Hadoop Administration Kafka Cluster Administration &amp; Maintenance Databricks Apache I</t>
+          <t>This job is with Moody's, an inclusive employer and a member of myGwork – the largest global platform for the LGBTQ business community. Please do not contact the recruiter directly. At Moody's, we unite the brightest minds to turn today’s risks into tomorrow’s opportunities. We do this by striving t</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/details/5804149618?utm_medium=api&amp;utm_source=447522e9</t>
+          <t>https://www.adzuna.in/land/ad/5846723030?se=xPWlIn6n8RG374tWD5Donw&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=A12DF7C02E8D43AB5777E0856BEFF63ACAB7EB16</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -531,25 +531,25 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-09-03 05:10:31</t>
+          <t>2026-09-03 09:59:43</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-09-03 09:50:48</t>
+          <t>2026-09-03 09:59:43</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>274b5127202b71d7582d</t>
+          <t>66dc2e5e20f98f9e760e</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>skill:Python, skill:Bash, skill:Kubernetes</t>
+          <t>no specific skill keywords matched (still passed role/location/experience filters)</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -567,32 +567,32 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>78a6d7560ddbd4caa774</t>
+          <t>d8e52bbb342dc8a0cd71</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Acme Services Private Limited</t>
+          <t>Moody's</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Staff Software Engineer</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Richmond Town, Bangalore</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Job Description: Build application-facing AI features powered by LLMs, agentic workflows, and AI orchestration platforms. Integrate with MLOps-managed agents and consume LLM capabilities through AI Gateway patterns including routing, authentication, policy controls, and logging. Design and implement</t>
+          <t>This job is with Moody's, an inclusive employer and a member of myGwork – the largest global platform for the LGBTQ business community. Please do not contact the recruiter directly. At Moody's, we unite the brightest minds to turn today’s risks into tomorrow’s opportunities. We do this by striving t</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/details/5863107008?utm_medium=api&amp;utm_source=447522e9</t>
+          <t>https://www.adzuna.in/land/ad/5846723078?se=xPWlIn6n8RG374tWD5Donw&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=E4A1A73C5F666ACB84BAE4E1985959AA9FF61296</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -602,25 +602,25 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-09-03 05:10:31</t>
+          <t>2026-09-03 09:59:43</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-09-03 09:50:48</t>
+          <t>2026-09-03 09:59:43</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>3337532b20885bd1775f</t>
+          <t>66dc2e5e20f98f9e760e</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>skill:LLM, skill:MCP, skill:AI Orchestration, skill:Tool Calling</t>
+          <t>no specific skill keywords matched (still passed role/location/experience filters)</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -638,32 +638,32 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>f65350a6483821dfdd3a</t>
+          <t>00542b536b013af3c1ea</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Acme Services Private Limited</t>
+          <t>Moody's</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Staff Software Engineer</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Richmond Town, Bangalore</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Job Description: Build and deploy production-grade AI and Agentic AI solutions for client business use cases. Design and implement AI agent workflows using LangGraph, CrewAI, and cloud-based agent platforms. Develop and manage AI/ML pipelines, including RAG, multi-agent orchestration, evaluation, an</t>
+          <t>This job is with Moody's, an inclusive employer and a member of myGwork – the largest global platform for the LGBTQ business community. Please do not contact the recruiter directly. At Moody's, we unite the brightest minds to turn today’s risks into tomorrow’s opportunities. We do this by striving t</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/details/5865169480?utm_medium=api&amp;utm_source=447522e9</t>
+          <t>https://www.adzuna.in/land/ad/5846723388?se=xPWlIn6n8RG374tWD5Donw&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=43BAAB4C2B9B91025B2C4E2EF1039AF52FAE195C</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -673,25 +673,25 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-09-03 05:10:31</t>
+          <t>2026-09-03 09:59:43</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-09-03 09:50:48</t>
+          <t>2026-09-03 09:59:43</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>1463f44c91d7b4c9c45f</t>
+          <t>66dc2e5e20f98f9e760e</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>skill:MCP, skill:RAG, skill:Multi-Agent Systems, skill:Agentic AI, skill:AI Agents, skill:Observability</t>
+          <t>no specific skill keywords matched (still passed role/location/experience filters)</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -709,73 +709,3137 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>058f011201829a910f1b</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Moody's</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Staff Software Engineer</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>This job is with Moody's, an inclusive employer and a member of myGwork – the largest global platform for the LGBTQ business community. Please do not contact the recruiter directly. At Moody's, we unite the brightest minds to turn today’s risks into tomorrow’s opportunities. We do this by striving t</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/land/ad/5846723080?se=xPWlIn6n8RG374tWD5Donw&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=BDD9C2926EC9D90B80A0CDAE02AC3B622B32FC99</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:59:43</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:59:43</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>66dc2e5e20f98f9e760e</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>no specific skill keywords matched (still passed role/location/experience filters)</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>9539dece673a2a0e582d</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Arcana</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Software Engineer in Test</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>We are looking for a meticulous SDET who will be responsible for the design and implementation of automated tests and test environments for Arcana. The engineer must have a passion for diving into data and technology, be a problem solver, and have a desire to improve software quality within a team e</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/land/ad/5864426564?se=xPWlIn6n8RG374tWD5Donw&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=B290C528C0913CA557D80924BA0AF30FE71A1A00</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:59:43</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:59:43</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>f60431bccffac2a157db</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>no specific skill keywords matched (still passed role/location/experience filters)</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>a612ea90186a9e7d8de2</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Recro</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Software Engineer - Browser Automation</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mission If you ask a hospital today how much a treatment will cost, the answer is usually: “We don’t know.” Not because providers don’t want to tell you but because patient cost is computed across insurance plans, negotiated rates, and billing rules that are fragmented, opaque, and not designed for </t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/land/ad/5864426312?se=xPWlIn6n8RG374tWD5Donw&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=A27346080A30C3E564878BC09AB7AD3C017DF8A2</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:59:43</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:59:43</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>bb4229ae4e92fd53fd70</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>no specific skill keywords matched (still passed role/location/experience filters)</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>c897ba7373753ad63fed</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Warner Bros. Discovery</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Staff Software Engineer - iOS</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>This job is with Warner Bros. Discovery, an inclusive employer and a member of myGwork – the largest global platform for the LGBTQ business community. Please do not contact the recruiter directly. Welcome to Warner Bros. Discovery… the stuff dreams are made of. Who We Are… When we say, “the stuff dr</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/land/ad/5838614193?se=xPWlIn6n8RG374tWD5Donw&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=9A92C6347994E53121C302383944CFFCF637848A</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:59:43</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:59:43</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>6c790a91ce0ffd7dd4b9</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>no specific skill keywords matched (still passed role/location/experience filters)</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>bb53da2c8f8302be4671</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Moody's</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Software Engineer - Sharepoint Developer</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>This job is with Moody's, an inclusive employer and a member of myGwork – the largest global platform for the LGBTQ business community. Please do not contact the recruiter directly. At Moody's, we unite the brightest minds to turn today’s risks into tomorrow’s opportunities. We do this by striving t</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/land/ad/5865064890?se=xPWlIn6n8RG374tWD5Donw&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=7D08E55F7B8119270271C16BDF7CB0165F3E88A9</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:59:43</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:59:43</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>2bf16fb064685a7ffe3b</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>no specific skill keywords matched (still passed role/location/experience filters)</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>56e7fcfc46d50e08e946</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>eBay</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Software Engineer Streaming/Messaging</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>This job is with eBay, an inclusive employer and a member of myGwork – the largest global platform for the LGBTQ business community. Please do not contact the recruiter directly. At eBay, we're more than a global ecommerce leader - we're changing the way the world shops and sells. Our platform empow</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/land/ad/5857251208?se=xPWlIn6n8RG374tWD5Donw&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=D2EDC0229B026B966CEF760E9377E8C7A3A5D261</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:59:43</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:59:43</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fb9977ca338517ea419e</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>no specific skill keywords matched (still passed role/location/experience filters)</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>e29352b5ddca57123a4b</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kyndryl</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Platform Engineer</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>This job is with Kyndryl, an inclusive employer and a member of myGwork – the largest global platform for the LGBTQ business community. Please do not contact the recruiter directly. Who We Are At Kyndryl, we run and reimagine the mission-critical technology systems that drive advantage for the world</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/land/ad/5855007034?se=XgEjI36n8RGYPeNUtjqvZg&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=83A2754BAF8C6CCAD9027F1D5977A1C5CB44300B</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:59:43</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:59:43</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>ceca84cf6d2ca557991f</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>no specific skill keywords matched (still passed role/location/experience filters)</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>c357f2150b2869afd7e5</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kyndryl</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Platform Engineer - Data</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>This job is with Kyndryl, an inclusive employer and a member of myGwork – the largest global platform for the LGBTQ business community. Please do not contact the recruiter directly. Who We Are At Kyndryl, we run and reimagine the mission-critical technology systems that drive advantage for the world</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/land/ad/5855007050?se=XgEjI36n8RGYPeNUtjqvZg&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=C4EED2A519F03E0B87055D11E8D44FFF3C83C9AE</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:59:43</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:59:43</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>0ddef43662b0a513eaff</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>no specific skill keywords matched (still passed role/location/experience filters)</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>20b9022020958ad97c5b</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kyndryl</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Platform Engineer - Data</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>This job is with Kyndryl, an inclusive employer and a member of myGwork – the largest global platform for the LGBTQ business community. Please do not contact the recruiter directly. Who We Are At Kyndryl, we run and reimagine the mission-critical technology systems that drive advantage for the world</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/land/ad/5855007011?se=XgEjI36n8RGYPeNUtjqvZg&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=2072E1F6EA4EA104D4C5F33605E51A05D7D97600</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:59:43</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:59:43</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>0ddef43662b0a513eaff</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>no specific skill keywords matched (still passed role/location/experience filters)</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>e266811f4bb678f943f3</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kyndryl</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>DevOps / Platform Engineer</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>This job is with Kyndryl, an inclusive employer and a member of myGwork – the largest global platform for the LGBTQ business community. Please do not contact the recruiter directly. Who We Are At Kyndryl, we run and reimagine the mission-critical technology systems that drive advantage for the world</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/land/ad/5837139061?se=XgEjI36n8RGYPeNUtjqvZg&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=5285674828FE37C646BCC77D46165795A7AC83F3</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:59:43</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:59:43</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>5639a74955a329af8fdb</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>no specific skill keywords matched (still passed role/location/experience filters)</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2f32d43081ee76a41d0a</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>eBay</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>AI Platform Engineer</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>This job is with eBay, an inclusive employer and a member of myGwork – the largest global platform for the LGBTQ business community. Please do not contact the recruiter directly. At eBay, we're more than a global ecommerce leader - we're changing the way the world shops and sells. Our platform empow</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/land/ad/5857982488?se=XgEjI36n8RGYPeNUtjqvZg&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=A746E3D6C2072081EB037DB5FF89DB2B1F4A7F7A</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:59:43</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:59:43</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>003a5b09f0f9cab65bcb</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>no specific skill keywords matched (still passed role/location/experience filters)</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>c5f8000b78f26d2458b2</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>eBay</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>AI Platform Engineer</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>This job is with eBay, an inclusive employer and a member of myGwork – the largest global platform for the LGBTQ business community. Please do not contact the recruiter directly. At eBay, we're more than a global ecommerce leader - we're changing the way the world shops and sells. Our platform empow</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/land/ad/5857982562?se=XgEjI36n8RGYPeNUtjqvZg&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=D215B0FD12910D6EA0FB670B7E4060E2013251A2</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:59:43</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:59:43</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>003a5b09f0f9cab65bcb</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>no specific skill keywords matched (still passed role/location/experience filters)</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>a594b8847c4fcf36dd31</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>eBay</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>AI Platform Engineer</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>This job is with eBay, an inclusive employer and a member of myGwork – the largest global platform for the LGBTQ business community. Please do not contact the recruiter directly. At eBay, we're more than a global ecommerce leader - we're changing the way the world shops and sells. Our platform empow</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/land/ad/5857251116?se=XgEjI36n8RGYPeNUtjqvZg&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=08120470A120A602552281268EC24E0672DD8DC2</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:59:43</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:59:43</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>003a5b09f0f9cab65bcb</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>no specific skill keywords matched (still passed role/location/experience filters)</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>543f539728eb8b213d62</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>eBay</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Sr Platform Engineer, Java Fmwk</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>This job is with eBay, an inclusive employer and a member of myGwork – the largest global platform for the LGBTQ business community. Please do not contact the recruiter directly. At eBay, we're more than a global ecommerce leader - we're changing the way the world shops and sells. Our platform empow</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/land/ad/5857251186?se=XgEjI36n8RGYPeNUtjqvZg&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=86E067A84B4608D56A8DF7DAC543EB1D3E73B398</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:59:43</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:59:43</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>aa0e96d98caef2fa536a</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>no specific skill keywords matched (still passed role/location/experience filters)</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>0c01c4c140da2ac12d0d</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>eBay</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>MTS 2, Software Engineer, Data Platforms</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>This job is with eBay, an inclusive employer and a member of myGwork – the largest global platform for the LGBTQ business community. Please do not contact the recruiter directly. At eBay, we're more than a global ecommerce leader - we're changing the way the world shops and sells. Our platform empow</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/land/ad/5857251152?se=XgEjI36n8RGYPeNUtjqvZg&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=F6ED6E5761AAB007E2A108EBC1289F6B09295EAC</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:59:43</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:59:43</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>46cb39c0bc105ab9f28b</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>no specific skill keywords matched (still passed role/location/experience filters)</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2464b37e117f06c8a647</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Kyndryl</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Software Engineer - Microsoft Power Platform Developer</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>This job is with Kyndryl, an inclusive employer and a member of myGwork – the largest global platform for the LGBTQ business community. Please do not contact the recruiter directly. Who We Are At Kyndryl, we run and reimagine the mission-critical technology systems that drive advantage for the world</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/land/ad/5837138735?se=XgEjI36n8RGYPeNUtjqvZg&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=30DB8AF6167416207F9C7D2B1D78CA8ED201388F</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:59:43</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:59:43</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>c9d99c912c70ba128422</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>no specific skill keywords matched (still passed role/location/experience filters)</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>cd8c00cdc93bdd72a9f8</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Kyndryl</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Software Engineer - Microsoft Power Platform Developer</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>This job is with Kyndryl, an inclusive employer and a member of myGwork – the largest global platform for the LGBTQ business community. Please do not contact the recruiter directly. Who We Are At Kyndryl, we run and reimagine the mission-critical technology systems that drive advantage for the world</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/land/ad/5841509246?se=XgEjI36n8RGYPeNUtjqvZg&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=77A93A263198B258FF86EBD054D2013BF2EF8C57</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:59:43</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:59:43</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>c9d99c912c70ba128422</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>no specific skill keywords matched (still passed role/location/experience filters)</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>0fa3d588c2f7472524a1</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Tekskills India Private Limited</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Platform Engineer</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>We are hiring an experienced Platform Engineer with strong expertise in Cloudera, Kafka, Databricks, Azure Synapse, PySpark, and Infrastructure Automation . Mandatory Skills Cloudera Platform Administration Cloudera Hadoop Administration Kafka Cluster Administration &amp; Maintenance Databricks Apache I</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/details/5804149618?utm_medium=api&amp;utm_source=447522e9</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>2026-09-03 05:10:31</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:59:43</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>274b5127202b71d7582d</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>30</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>skill:Python, skill:Bash, skill:Kubernetes</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>92edb3c5ff36538976a8</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Ema</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Platform Engineer</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>About Ema Ema is building the world’s leading Agentic AI platform to transform enterprise productivity. We enable organizations to delegate repetitive tasks to Ema, the Universal AI Employee, delivering 10x gains in workforce efficiency, across functions. Founded by former executives from Google, Co</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/details/5841942939?utm_medium=api&amp;utm_source=447522e9</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:59:43</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:59:43</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>5495eb964a9b85d9b44b</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>10</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>skill:Agentic AI</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>697f79c89cfd42d31537</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Teradata</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Platform Engineer</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Our Company At Teradata, we believe that people thrive when empowered with better information. Teradata Autonomous Knowledge Platform activates enterprise intelligence by unifying data, knowledge and business context to achieve tangible outcomes. With Teradata, organizations can provide agents with </t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/details/5860807556?utm_medium=api&amp;utm_source=447522e9</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:59:43</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:59:43</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>41695566aaf8ba5f1534</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>no specific skill keywords matched (still passed role/location/experience filters)</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>e2e2bcaf85a138e3e222</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Axi</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Platform Engineer</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Please note that we will only be able to accept candidates who have the appropriate rights and documentation for employment in India. Who we are. Axi is a leading global provider of margin and deliverable Foreign Exchange, Contracts for Difference (CFDs), and Financial Spread betting. Our business h</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/details/5703939765?utm_medium=api&amp;utm_source=447522e9</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:59:43</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:59:43</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>7b987ebc25ff07153a69</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>no specific skill keywords matched (still passed role/location/experience filters)</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>de0945b7a98928cd69a6</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Finastra Technology</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Platform Engineer</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Who are we? At Finastra, we’re a global leader in financial services software, dedicated to expanding access to financial services and shaping what’s next for the industry. Our technology powers mission‑critical solutions across Lending, Payments and Universal Banking, supporting over 7,000 customer</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/details/5858359807?utm_medium=api&amp;utm_source=447522e9</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:59:43</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:59:43</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>759c43c17fe4627449bd</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>no specific skill keywords matched (still passed role/location/experience filters)</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>86b6124a4b8cdec681b6</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Aryaka</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Platform Engineer</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Description Platform Engineer (Java Full Stack ) As a FullStack Developer , you should have strong analytical skills, a well-rounded understanding of both front-end and back-end development, and a passion for problem-solving. Location : Bangalore, India You will have - Bachelor’s degree required. Mi</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/details/5557596032?utm_medium=api&amp;utm_source=447522e9</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:59:43</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:59:43</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>34148979a4e39eab8879</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>no specific skill keywords matched (still passed role/location/experience filters)</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>65e49cef69dea487b58a</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Kyndryl</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Platform Engineer</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Partially Remote Bangalore, Karnataka, India INEMTECH PUNE - ETZ Chennai, Tamil Nadu, India INDIVYA HYD - DIVYASHREE IN152015 NOIDA (IN152015) ARTHA INFRATE Full time R-66887 Who We Are At Kyndryl, we run and reimagine the mission-critical technology systems that drive advantage for the world's lead</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/details/5856447377?utm_medium=api&amp;utm_source=447522e9</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:59:43</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:59:43</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>2820ee427366f09ef1ec</t>
+        </is>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>no specific skill keywords matched (still passed role/location/experience filters)</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>16c6e859214c7ebdbdac</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Agentic AI Engineer</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">This job is with HP, an inclusive employer and a member of myGwork – the largest global platform for the LGBTQ business community. Please do not contact the recruiter directly. Agentic AI Engineer Description - Job Summary This role is responsible for leading the design and execution of advanced AI </t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/land/ad/5847959683?se=wg2FI36n8RG374tWD5Donw&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=44FCE51978FD48A3291A05FC0AFB8C9CBD5612B2</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:59:43</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:59:43</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>595e5ce0c414149729d2</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
+        <v>10</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>skill:Agentic AI</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>f797151a1198dd7bca67</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Standard Chartered Bank</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>AI Engineer (India, China)</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>This job is with Standard Chartered Bank, an inclusive employer and a member of myGwork – the largest global platform for the LGBTQ business community. Please do not contact the recruiter directly. Job Summary This role could be based in India or China. When you start the application process you wil</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/land/ad/5854537872?se=wg2FI36n8RG374tWD5Donw&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=71FDDD42F1439DDFA00C96C1342A4501A4014B38</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:59:43</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:59:43</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>3b8c8ab85bf42ee3a205</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>no specific skill keywords matched (still passed role/location/experience filters)</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>383b7e154def0e3aad2e</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>eBay</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>AI Platform Engineer</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>This job is with eBay, an inclusive employer and a member of myGwork – the largest global platform for the LGBTQ business community. Please do not contact the recruiter directly. At eBay, we're more than a global ecommerce leader - we're changing the way the world shops and sells. Our platform empow</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/land/ad/5857982562?se=wg2FI36n8RG374tWD5Donw&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=D215B0FD12910D6EA0FB670B7E4060E2013251A2</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:59:43</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:59:43</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>003a5b09f0f9cab65bcb</t>
+        </is>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>no specific skill keywords matched (still passed role/location/experience filters)</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>84267bff351951686970</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>eBay</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>AI Platform Engineer</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>This job is with eBay, an inclusive employer and a member of myGwork – the largest global platform for the LGBTQ business community. Please do not contact the recruiter directly. At eBay, we're more than a global ecommerce leader - we're changing the way the world shops and sells. Our platform empow</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/land/ad/5857982488?se=wg2FI36n8RG374tWD5Donw&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=A746E3D6C2072081EB037DB5FF89DB2B1F4A7F7A</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:59:43</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:59:43</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>003a5b09f0f9cab65bcb</t>
+        </is>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>no specific skill keywords matched (still passed role/location/experience filters)</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>6fb4946bf27e505d27e1</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>eBay</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>AI Platform Engineer</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>This job is with eBay, an inclusive employer and a member of myGwork – the largest global platform for the LGBTQ business community. Please do not contact the recruiter directly. At eBay, we're more than a global ecommerce leader - we're changing the way the world shops and sells. Our platform empow</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/land/ad/5857251116?se=wg2FI36n8RG374tWD5Donw&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=08120470A120A602552281268EC24E0672DD8DC2</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:59:43</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:59:43</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>003a5b09f0f9cab65bcb</t>
+        </is>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>no specific skill keywords matched (still passed role/location/experience filters)</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>78a6d7560ddbd4caa774</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Acme Services Private Limited</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Richmond Town, Bangalore</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Job Description: Build application-facing AI features powered by LLMs, agentic workflows, and AI orchestration platforms. Integrate with MLOps-managed agents and consume LLM capabilities through AI Gateway patterns including routing, authentication, policy controls, and logging. Design and implement</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/details/5863107008?utm_medium=api&amp;utm_source=447522e9</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>2026-09-03 05:10:31</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:59:43</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>3337532b20885bd1775f</t>
+        </is>
+      </c>
+      <c r="K34" t="n">
+        <v>40</v>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>skill:LLM, skill:MCP, skill:AI Orchestration, skill:Tool Calling</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>f65350a6483821dfdd3a</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Acme Services Private Limited</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Richmond Town, Bangalore</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Job Description: Build and deploy production-grade AI and Agentic AI solutions for client business use cases. Design and implement AI agent workflows using LangGraph, CrewAI, and cloud-based agent platforms. Develop and manage AI/ML pipelines, including RAG, multi-agent orchestration, evaluation, an</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/details/5865169480?utm_medium=api&amp;utm_source=447522e9</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>2026-09-03 05:10:31</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:59:43</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>1463f44c91d7b4c9c45f</t>
+        </is>
+      </c>
+      <c r="K35" t="n">
+        <v>60</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>skill:MCP, skill:RAG, skill:Multi-Agent Systems, skill:Agentic AI, skill:AI Agents, skill:Observability</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
           <t>758e789b17e2f7dd6c51</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>Jothishi Online and Advertising Services Private Limited</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>AI Engineer</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>Bangalore, Karnataka</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>AI ENGINEER – RETROGRADE AI Generative AI | LLMs | RAG | AI Agents | Vedic Astrology Company: JOTHISHI Online &amp; Advertising Services Pvt. Ltd. Product: RetroGrade AI Website: https://retrograde.co.in/ Location: Bengaluru / Hybrid / Remote Employment: Full-Time About RetroGrade AI RetroGrade AI , fro</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>https://www.adzuna.in/details/5842544539?utm_medium=api&amp;utm_source=447522e9</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>adzuna</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t>2026-09-03 05:10:31</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2026-09-03 09:50:48</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:59:43</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
         <is>
           <t>088a26264467b471f752</t>
         </is>
       </c>
-      <c r="K5" t="n">
+      <c r="K36" t="n">
         <v>20</v>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="L36" t="inlineStr">
         <is>
           <t>skill:RAG, skill:AI Agents</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>d8522750bd2d5068740c</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>MyData Insights Private Limited</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>AI engineer</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Description We are looking for a talented AI Engineer to join MyData Insights Private Limited, a leading company in the Information Technology sector. As an AI Engineer, you will play a crucial role in developing and implementing cutting-edge artificial intelligence solutions. Your work will be inst</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/details/5503837785?utm_medium=api&amp;utm_source=447522e9</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:59:43</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:59:43</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>33311190bd5f9f970705</t>
+        </is>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>no specific skill keywords matched (still passed role/location/experience filters)</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>74361c3c5b6a7bd8f0c9</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Sophos</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Full Stack Software Engineer</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>&amp;nbsp;...What You Will Do  We are looking for a highly motivated Full Stack &lt;b&gt;Software Engineer &lt;/b&gt;to join our engineering team and contribute to the development of next-generation web applications, UI frameworks, and developer platforms. The ideal candidate should have strong experience...&amp;nbsp;</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>https://jooble.org/desc/-796507398843211532?ckey=software+engineer&amp;rgn=55126&amp;pos=1&amp;groupId=1087&amp;elckey=-2548016414711590688&amp;p=1&amp;aq=3422438110858789038&amp;cid=18943&amp;jobAge=891&amp;brelb=15&amp;bscr=146.32024&amp;scr=146.32024</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>jooble</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:59:43</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:59:43</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>345a1a1939d28110d6c0</t>
+        </is>
+      </c>
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>no specific skill keywords matched (still passed role/location/experience filters)</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>b5b99a577168471b071c</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>SaidGig</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Full-Stack Software Engineer, India</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>&amp;nbsp;...Role Overview  Build and stress-test production &lt;b&gt;software &lt;/b&gt;that brings frontier large language models into real applications before release. You will work directly with an &lt;b&gt;engineering &lt;/b&gt;manager on fast-moving generative AI projects, ramp up quickly, and contribute working...&amp;nbsp;</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>https://jooble.org/away/-4293671604513188386?p=1&amp;pos=2&amp;rgn=55126&amp;cid=18943&amp;ckey=software+engineer&amp;jobAge=555&amp;brelb=15&amp;scr=145.33661&amp;bscr=145.33661&amp;aq=3422438110858789038&amp;elckey=-2548016414711590688</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>jooble</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:59:43</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:59:43</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>96b20e55f4c7bfdd2bfa</t>
+        </is>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>no specific skill keywords matched (still passed role/location/experience filters)</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>d4645de8149a3e1bc561</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>dscout</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>&amp;nbsp;...Building AI-native products is a different problem than building deterministic &lt;b&gt;software:&lt;/b&gt; the same input won't always produce the same output. Good product &lt;b&gt;engineering &lt;/b&gt;here means designing experiences that stay useful, trustworthy, and easy to understand even when the AI...&amp;nbs</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>https://jooble.org/away/9161242534232820748?p=1&amp;pos=7&amp;rgn=55126&amp;cid=18943&amp;ckey=software+engineer&amp;jobAge=291&amp;brelb=15&amp;scr=100.0383&amp;bscr=100.0383&amp;aq=3422438110858789038&amp;elckey=-2548016414711590688</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>jooble</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:59:43</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:59:43</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>b6c492cc480a7d5849df</t>
+        </is>
+      </c>
+      <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>no specific skill keywords matched (still passed role/location/experience filters)</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>60b939052e250e9bb2da</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Mastercard</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Software Engineer I</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>&amp;nbsp;...set of products and services that help people, businesses and governments realize their greatest potential.  Title and Summary  &lt;b&gt;Software Engineer &lt;/b&gt;I 
+ Who is Mastercard? 
+ Mastercard is a global technology company in the payments industry. Our mission is to connect and...&amp;nbsp;</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>https://jooble.org/away/7995986347102170187?p=1&amp;pos=8&amp;rgn=55126&amp;cid=18943&amp;ckey=software+engineer&amp;jobAge=387&amp;brelb=15&amp;scr=99.79796&amp;bscr=99.79796&amp;aq=3422438110858789038&amp;elckey=-2548016414711590688</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>jooble</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:59:43</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:59:43</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>b9acbee7d077854d07e3</t>
+        </is>
+      </c>
+      <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>no specific skill keywords matched (still passed role/location/experience filters)</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>0f0c261f499c9a64d4ae</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Mastercard</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Software engineer</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>&amp;nbsp;...set of products and services that help people, businesses and governments realize their greatest potential.  Title and Summary  &lt;b&gt;Software engineer &lt;/b&gt;
+ Overview 
+ This role operates within a globally distributed delivery model, partnering closely with established onshore...&amp;nbsp;</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>https://jooble.org/away/2894123168819324865?p=1&amp;pos=9&amp;rgn=55126&amp;cid=18943&amp;ckey=software+engineer&amp;jobAge=387&amp;brelb=15&amp;scr=99.68298&amp;bscr=99.68298&amp;aq=3422438110858789038&amp;elckey=-2548016414711590688</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>jooble</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:59:43</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:59:43</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>40ba657d8dba95abbba8</t>
+        </is>
+      </c>
+      <c r="K42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>no specific skill keywords matched (still passed role/location/experience filters)</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>0edae5b9857a477ffd98</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Bugcrowd</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Software Engineer - Mayhem Engineering</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>&amp;nbsp;...Job Summary  We are looking for a detail-oriented and analytical &lt;b&gt;Software Engineer &lt;/b&gt;to join our Mayhem Engineering team. In this role, you will be responsible for the design and development of our cloud native, API-first platform for Mayhem, our autonomous application security...&amp;nbsp</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>https://jooble.org/away/-7118131228584181828?p=1&amp;pos=12&amp;rgn=55126&amp;cid=18943&amp;ckey=software+engineer&amp;jobAge=699&amp;brelb=15&amp;scr=96.20126&amp;bscr=96.20126&amp;aq=3422438110858789038&amp;elckey=-2548016414711590688</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>jooble</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:59:43</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:59:43</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>b0697f4bd6426d8ace73</t>
+        </is>
+      </c>
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>no specific skill keywords matched (still passed role/location/experience filters)</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>311746dda22698ab5ca6</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Shipbob</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Software Development Engineer III</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>&amp;nbsp;...Role Description:  As a  &lt;b&gt;Software &lt;/b&gt;Development &lt;b&gt;Engineer &lt;/b&gt;III  at ShipBob, you will be primarily responsible for the development of production level software in coordination with your team. You will work very closely with Product Owners and your Engineering Manager. Being...&amp;nbsp</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>https://jooble.org/away/2586762583651071387?p=1&amp;pos=14&amp;rgn=55126&amp;cid=18943&amp;ckey=software+engineer&amp;jobAge=891&amp;brelb=15&amp;scr=96.1237&amp;bscr=96.1237&amp;aq=3422438110858789038&amp;elckey=-2548016414711590688</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>jooble</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:59:43</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:59:43</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>9f11b97acc59531516f7</t>
+        </is>
+      </c>
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>no specific skill keywords matched (still passed role/location/experience filters)</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>d6564fd5edfad2ecc606</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Paxos</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Data Platform Engineer</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>&amp;nbsp;...Mastercard and Interactive Brokers. 
+ About the team  The Data &lt;b&gt;Engineering &lt;/b&gt;team at Paxos builds and maintains the data infrastructure...&amp;nbsp;&amp;nbsp;...operational efficiencies. By continuously enhancing our data &lt;b&gt;platform,&lt;/b&gt; we drive innovation, optimize costs, and unlock new re</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>https://jooble.org/desc/-7539382523141682190?ckey=platform+engineer&amp;rgn=55126&amp;pos=7&amp;groupId=44066&amp;elckey=2196737102483659963&amp;p=1&amp;aq=2295900989087971703&amp;cid=18943&amp;jobAge=387&amp;brelb=15&amp;bscr=43.929035&amp;scr=43.929035</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>jooble</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:59:43</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:59:43</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>dd1cf4f3b8d9944df197</t>
+        </is>
+      </c>
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>no specific skill keywords matched (still passed role/location/experience filters)</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>361b80f98f49a136951a</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Mastercard</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Site Reliability Engineer II</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>&amp;nbsp;...and services that help people, businesses and governments realize their greatest potential.  Title and Summary  Site Reliability &lt;b&gt;Engineer &lt;/b&gt;II 
+ Site Reliability Engineer II 
+ Corporate Security Responsibility  All activities involving access to Mastercard assets, information...&amp;nbsp</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>https://jooble.org/away/284029486554793268?p=1&amp;pos=12&amp;rgn=55126&amp;cid=18943&amp;ckey=platform+engineer&amp;jobAge=387&amp;brelb=15&amp;scr=16.958855&amp;bscr=16.958855&amp;aq=2295900989087971703&amp;elckey=2196737102483659963</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>jooble</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:59:43</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:59:43</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>ce766b8fbeae73b47bc3</t>
+        </is>
+      </c>
+      <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>no specific skill keywords matched (still passed role/location/experience filters)</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>dd1969608ac7bb5124d9</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Mastercard</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Site Reliability Engineer I</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>&amp;nbsp;...their greatest potential.  Title and Summary  Site Reliability &lt;b&gt;Engineer &lt;/b&gt;I 
+ Job Description Summary 
+ Job Title 
+ Site Reliability Engineer...&amp;nbsp;&amp;nbsp;...Operations SRE, we are responsible for ensuring that our &lt;b&gt;platform &lt;/b&gt;is stable and healthy. We break down barriers to ru</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>https://jooble.org/away/5898814598423247422?p=1&amp;pos=15&amp;rgn=55126&amp;cid=18943&amp;ckey=platform+engineer&amp;jobAge=507&amp;brelb=15&amp;scr=16.81093&amp;bscr=16.81093&amp;aq=2295900989087971703&amp;elckey=2196737102483659963</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>jooble</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:59:43</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:59:43</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>261c2df44dbd387ba937</t>
+        </is>
+      </c>
+      <c r="K47" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>no specific skill keywords matched (still passed role/location/experience filters)</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>b6642f72e1c4e49c72b8</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Mrsool</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Site Reliability Engineer II</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>&amp;nbsp;...convenience meets innovation! As one of the largest delivery &lt;b&gt;platforms &lt;/b&gt;in the Middle East and North Africa (MENA) region, Mrsool has...&amp;nbsp;&amp;nbsp;...of a button. 
+ We are seeking an experienced Site Reliability &lt;b&gt;Engineer &lt;/b&gt;(SRE) to join our team. As an SRE, you will play a crit</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>https://jooble.org/desc/1618749610628369248?ckey=platform+engineer&amp;rgn=55126&amp;pos=16&amp;groupId=44066&amp;elckey=2196737102483659963&amp;p=1&amp;aq=2295900989087971703&amp;cid=18943&amp;jobAge=699&amp;brelb=15&amp;bscr=16.81093&amp;scr=16.81093</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>jooble</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:59:43</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:59:43</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>a799a955ccfa008e56d7</t>
+        </is>
+      </c>
+      <c r="K48" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>no specific skill keywords matched (still passed role/location/experience filters)</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/vignesh_jobs.xlsx
+++ b/data/vignesh_jobs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O42"/>
+  <dimension ref="A1:O45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -496,7 +496,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>858e98f6bab5e9ef3f77</t>
+          <t>210c15cea861a52cfbaf</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -521,7 +521,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5846723030?se=0ObuTIGn8RGxLcPzt0M5RA&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=A12DF7C02E8D43AB5777E0856BEFF63ACAB7EB16</t>
+          <t>https://www.adzuna.in/land/ad/5846723030?se=RJejXYOn8RG378CicPtDfg&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=A12DF7C02E8D43AB5777E0856BEFF63ACAB7EB16</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -531,12 +531,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-09-03 10:22:23</t>
+          <t>2026-09-03 10:37:46</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-09-03 10:22:23</t>
+          <t>2026-09-03 10:37:46</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -567,7 +567,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>9d6e0815ac20080643a3</t>
+          <t>6b5ea1c172a150f0bc54</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -592,7 +592,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5846723078?se=0ObuTIGn8RGxLcPzt0M5RA&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=E4A1A73C5F666ACB84BAE4E1985959AA9FF61296</t>
+          <t>https://www.adzuna.in/land/ad/5846723078?se=RJejXYOn8RG378CicPtDfg&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=E4A1A73C5F666ACB84BAE4E1985959AA9FF61296</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -602,12 +602,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-09-03 10:22:23</t>
+          <t>2026-09-03 10:37:46</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-09-03 10:22:23</t>
+          <t>2026-09-03 10:37:46</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -638,7 +638,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>b1d5952b8b115e680238</t>
+          <t>8d4cc96dcbb276bb21da</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5846723388?se=0ObuTIGn8RGxLcPzt0M5RA&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=43BAAB4C2B9B91025B2C4E2EF1039AF52FAE195C</t>
+          <t>https://www.adzuna.in/land/ad/5846723388?se=RJejXYOn8RG378CicPtDfg&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=43BAAB4C2B9B91025B2C4E2EF1039AF52FAE195C</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -673,12 +673,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-09-03 10:22:23</t>
+          <t>2026-09-03 10:37:46</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-09-03 10:22:23</t>
+          <t>2026-09-03 10:37:46</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -709,7 +709,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>d462a01988c34a3013ca</t>
+          <t>08115dabf6d1b27272aa</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5846723080?se=0ObuTIGn8RGxLcPzt0M5RA&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=BDD9C2926EC9D90B80A0CDAE02AC3B622B32FC99</t>
+          <t>https://www.adzuna.in/land/ad/5846723080?se=RJejXYOn8RG378CicPtDfg&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=BDD9C2926EC9D90B80A0CDAE02AC3B622B32FC99</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -744,12 +744,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-09-03 10:22:23</t>
+          <t>2026-09-03 10:37:46</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-09-03 10:22:23</t>
+          <t>2026-09-03 10:37:46</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -780,7 +780,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>d6eb71d0ee2a621c2473</t>
+          <t>727041a7e3718f343702</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -805,7 +805,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5864426564?se=0ObuTIGn8RGxLcPzt0M5RA&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=B290C528C0913CA557D80924BA0AF30FE71A1A00</t>
+          <t>https://www.adzuna.in/land/ad/5864426564?se=RJejXYOn8RG378CicPtDfg&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=B290C528C0913CA557D80924BA0AF30FE71A1A00</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-09-03 10:22:23</t>
+          <t>2026-09-03 10:37:46</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-09-03 10:22:23</t>
+          <t>2026-09-03 10:37:46</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -851,7 +851,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>a3e1e206aee95d22695f</t>
+          <t>bed86644c34f4c005d35</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5864426312?se=0ObuTIGn8RGxLcPzt0M5RA&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=A27346080A30C3E564878BC09AB7AD3C017DF8A2</t>
+          <t>https://www.adzuna.in/land/ad/5864426312?se=RJejXYOn8RG378CicPtDfg&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=A27346080A30C3E564878BC09AB7AD3C017DF8A2</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -886,12 +886,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-09-03 10:22:23</t>
+          <t>2026-09-03 10:37:46</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-09-03 10:22:23</t>
+          <t>2026-09-03 10:37:46</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -922,7 +922,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>30e3c9ff316c794b1b00</t>
+          <t>e22d57f564e6be323c23</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5838614193?se=0ObuTIGn8RGxLcPzt0M5RA&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=9A92C6347994E53121C302383944CFFCF637848A</t>
+          <t>https://www.adzuna.in/land/ad/5838614193?se=RJejXYOn8RG378CicPtDfg&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=9A92C6347994E53121C302383944CFFCF637848A</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -957,12 +957,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-09-03 10:22:23</t>
+          <t>2026-09-03 10:37:46</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-09-03 10:22:23</t>
+          <t>2026-09-03 10:37:46</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -993,7 +993,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3c3827d23d4a911c5f4a</t>
+          <t>90ac829e0e0579f886b7</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5865064890?se=0ObuTIGn8RGxLcPzt0M5RA&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=7D08E55F7B8119270271C16BDF7CB0165F3E88A9</t>
+          <t>https://www.adzuna.in/land/ad/5865064890?se=RJejXYOn8RG378CicPtDfg&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=7D08E55F7B8119270271C16BDF7CB0165F3E88A9</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-09-03 10:22:23</t>
+          <t>2026-09-03 10:37:46</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-09-03 10:22:23</t>
+          <t>2026-09-03 10:37:46</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1064,7 +1064,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>f0f1efa680ba773b4a6d</t>
+          <t>00836077b2959f1e7824</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5857251208?se=0ObuTIGn8RGxLcPzt0M5RA&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=D2EDC0229B026B966CEF760E9377E8C7A3A5D261</t>
+          <t>https://www.adzuna.in/land/ad/5857251208?se=RJejXYOn8RG378CicPtDfg&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=D2EDC0229B026B966CEF760E9377E8C7A3A5D261</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1099,12 +1099,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-09-03 10:22:23</t>
+          <t>2026-09-03 10:37:46</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-09-03 10:22:23</t>
+          <t>2026-09-03 10:37:46</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1135,7 +1135,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>24dbeb3cf4fff113ad77</t>
+          <t>57b3b6ad55a818e755a8</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5855007034?se=BOovTYGn8RG374tWD5Donw&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=83A2754BAF8C6CCAD9027F1D5977A1C5CB44300B</t>
+          <t>https://www.adzuna.in/land/ad/5855007034?se=RjrlXYOn8RG374tWD5Donw&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=83A2754BAF8C6CCAD9027F1D5977A1C5CB44300B</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-09-03 10:22:23</t>
+          <t>2026-09-03 10:37:46</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-09-03 10:22:23</t>
+          <t>2026-09-03 10:37:46</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1206,7 +1206,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>c39952c3676479083294</t>
+          <t>71750aceccf0ed1d2c1b</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5855007050?se=BOovTYGn8RG374tWD5Donw&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=C4EED2A519F03E0B87055D11E8D44FFF3C83C9AE</t>
+          <t>https://www.adzuna.in/land/ad/5855007050?se=RjrlXYOn8RG374tWD5Donw&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=C4EED2A519F03E0B87055D11E8D44FFF3C83C9AE</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-09-03 10:22:23</t>
+          <t>2026-09-03 10:37:46</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026-09-03 10:22:23</t>
+          <t>2026-09-03 10:37:46</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1277,7 +1277,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>297cc153849cf41b311f</t>
+          <t>4107de89a1399d76a424</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5855007011?se=BOovTYGn8RG374tWD5Donw&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=2072E1F6EA4EA104D4C5F33605E51A05D7D97600</t>
+          <t>https://www.adzuna.in/land/ad/5855007011?se=RjrlXYOn8RG374tWD5Donw&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=2072E1F6EA4EA104D4C5F33605E51A05D7D97600</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1312,12 +1312,12 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-09-03 10:22:23</t>
+          <t>2026-09-03 10:37:46</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026-09-03 10:22:23</t>
+          <t>2026-09-03 10:37:46</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1348,7 +1348,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>b6fa9018127613b9d16d</t>
+          <t>c0087f9cf87d470f0815</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5837139061?se=BOovTYGn8RG374tWD5Donw&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=5285674828FE37C646BCC77D46165795A7AC83F3</t>
+          <t>https://www.adzuna.in/land/ad/5837139061?se=RjrlXYOn8RG374tWD5Donw&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=5285674828FE37C646BCC77D46165795A7AC83F3</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1383,12 +1383,12 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-09-03 10:22:23</t>
+          <t>2026-09-03 10:37:46</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2026-09-03 10:22:23</t>
+          <t>2026-09-03 10:37:46</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1419,7 +1419,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>085f2f6dc4292be94e6d</t>
+          <t>7d8120415b6fac1d2e9f</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1444,7 +1444,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5857982488?se=BOovTYGn8RG374tWD5Donw&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=A746E3D6C2072081EB037DB5FF89DB2B1F4A7F7A</t>
+          <t>https://www.adzuna.in/land/ad/5857982488?se=RjrlXYOn8RG374tWD5Donw&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=A746E3D6C2072081EB037DB5FF89DB2B1F4A7F7A</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-09-03 10:22:23</t>
+          <t>2026-09-03 10:37:46</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2026-09-03 10:22:23</t>
+          <t>2026-09-03 10:37:46</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1490,7 +1490,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>4d3f2fd1a84e5ed1435b</t>
+          <t>31a99f0e429024e8eaf2</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1515,7 +1515,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5857982562?se=BOovTYGn8RG374tWD5Donw&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=D215B0FD12910D6EA0FB670B7E4060E2013251A2</t>
+          <t>https://www.adzuna.in/land/ad/5857982562?se=RjrlXYOn8RG374tWD5Donw&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=D215B0FD12910D6EA0FB670B7E4060E2013251A2</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1525,12 +1525,12 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-09-03 10:22:23</t>
+          <t>2026-09-03 10:37:46</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2026-09-03 10:22:23</t>
+          <t>2026-09-03 10:37:46</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1561,7 +1561,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>479cd4f90c1a2dcc37e2</t>
+          <t>227e67145cbc37e43c64</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5857251116?se=BOovTYGn8RG374tWD5Donw&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=08120470A120A602552281268EC24E0672DD8DC2</t>
+          <t>https://www.adzuna.in/land/ad/5857251116?se=RjrlXYOn8RG374tWD5Donw&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=08120470A120A602552281268EC24E0672DD8DC2</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-09-03 10:22:23</t>
+          <t>2026-09-03 10:37:46</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2026-09-03 10:22:23</t>
+          <t>2026-09-03 10:37:46</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1632,7 +1632,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>9ce40030f03bd398086a</t>
+          <t>3ba20c45590adf90c0a1</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1657,7 +1657,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5857251186?se=BOovTYGn8RG374tWD5Donw&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=86E067A84B4608D56A8DF7DAC543EB1D3E73B398</t>
+          <t>https://www.adzuna.in/land/ad/5857251186?se=RjrlXYOn8RG374tWD5Donw&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=86E067A84B4608D56A8DF7DAC543EB1D3E73B398</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1667,12 +1667,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-09-03 10:22:23</t>
+          <t>2026-09-03 10:37:46</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2026-09-03 10:22:23</t>
+          <t>2026-09-03 10:37:46</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1703,7 +1703,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0190019fe02a4b937502</t>
+          <t>d56d7fc4f8fc3d222e27</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5857251152?se=BOovTYGn8RG374tWD5Donw&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=F6ED6E5761AAB007E2A108EBC1289F6B09295EAC</t>
+          <t>https://www.adzuna.in/land/ad/5857251152?se=RjrlXYOn8RG374tWD5Donw&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=F6ED6E5761AAB007E2A108EBC1289F6B09295EAC</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1738,12 +1738,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-09-03 10:22:23</t>
+          <t>2026-09-03 10:37:46</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2026-09-03 10:22:23</t>
+          <t>2026-09-03 10:37:46</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1774,7 +1774,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>29db8b035d4c828243dd</t>
+          <t>591ea05c1c1ceb520697</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1799,7 +1799,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5837138735?se=BOovTYGn8RG374tWD5Donw&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=30DB8AF6167416207F9C7D2B1D78CA8ED201388F</t>
+          <t>https://www.adzuna.in/land/ad/5837138735?se=RjrlXYOn8RG374tWD5Donw&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=30DB8AF6167416207F9C7D2B1D78CA8ED201388F</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-09-03 10:22:23</t>
+          <t>2026-09-03 10:37:46</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2026-09-03 10:22:23</t>
+          <t>2026-09-03 10:37:46</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1845,7 +1845,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>143f58fe1a3133da72db</t>
+          <t>ed5c192f469451562a35</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1870,7 +1870,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5841509246?se=BOovTYGn8RG374tWD5Donw&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=77A93A263198B258FF86EBD054D2013BF2EF8C57</t>
+          <t>https://www.adzuna.in/land/ad/5841509246?se=RjrlXYOn8RG374tWD5Donw&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=77A93A263198B258FF86EBD054D2013BF2EF8C57</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-09-03 10:22:23</t>
+          <t>2026-09-03 10:37:46</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2026-09-03 10:22:23</t>
+          <t>2026-09-03 10:37:46</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2026-09-03 10:22:23</t>
+          <t>2026-09-03 10:37:46</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2027,7 +2027,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2026-09-03 10:22:23</t>
+          <t>2026-09-03 10:37:46</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2098,7 +2098,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2026-09-03 10:22:23</t>
+          <t>2026-09-03 10:37:46</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2169,7 +2169,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2026-09-03 10:22:23</t>
+          <t>2026-09-03 10:37:46</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2240,7 +2240,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2026-09-03 10:22:23</t>
+          <t>2026-09-03 10:37:46</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2311,7 +2311,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2026-09-03 10:22:23</t>
+          <t>2026-09-03 10:37:46</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2026-09-03 10:22:23</t>
+          <t>2026-09-03 10:37:46</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2413,7 +2413,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ae861f7de47a9c20a718</t>
+          <t>6302323b11e6e991b422</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2438,7 +2438,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5847959683?se=JBFwTYGn8RGYPeNUtjqvZg&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=44FCE51978FD48A3291A05FC0AFB8C9CBD5612B2</t>
+          <t>https://www.adzuna.in/land/ad/5847959683?se=fBopXoOn8RGYPeNUtjqvZg&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=44FCE51978FD48A3291A05FC0AFB8C9CBD5612B2</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-09-03 10:22:23</t>
+          <t>2026-09-03 10:37:46</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2026-09-03 10:22:23</t>
+          <t>2026-09-03 10:37:46</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2484,7 +2484,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>b35867fb09ab72c13256</t>
+          <t>b7ab0a173036fc899f01</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2509,7 +2509,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5854537872?se=JBFwTYGn8RGYPeNUtjqvZg&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=71FDDD42F1439DDFA00C96C1342A4501A4014B38</t>
+          <t>https://www.adzuna.in/land/ad/5854537872?se=fBopXoOn8RGYPeNUtjqvZg&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=71FDDD42F1439DDFA00C96C1342A4501A4014B38</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-09-03 10:22:23</t>
+          <t>2026-09-03 10:37:46</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2026-09-03 10:22:23</t>
+          <t>2026-09-03 10:37:46</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2555,7 +2555,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>9c7d91010ace614834e4</t>
+          <t>13c12bcdd49faab19e07</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2580,7 +2580,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5857982562?se=JBFwTYGn8RGYPeNUtjqvZg&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=D215B0FD12910D6EA0FB670B7E4060E2013251A2</t>
+          <t>https://www.adzuna.in/land/ad/5857982562?se=fBopXoOn8RGYPeNUtjqvZg&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=D215B0FD12910D6EA0FB670B7E4060E2013251A2</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2590,12 +2590,12 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-09-03 10:22:23</t>
+          <t>2026-09-03 10:37:46</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2026-09-03 10:22:23</t>
+          <t>2026-09-03 10:37:46</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2626,7 +2626,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ddc9af48506b4eda16c4</t>
+          <t>3ae8ed70dfbd34cb7442</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2651,7 +2651,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5857982488?se=JBFwTYGn8RGYPeNUtjqvZg&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=A746E3D6C2072081EB037DB5FF89DB2B1F4A7F7A</t>
+          <t>https://www.adzuna.in/land/ad/5857982488?se=fBopXoOn8RGYPeNUtjqvZg&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=A746E3D6C2072081EB037DB5FF89DB2B1F4A7F7A</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2661,12 +2661,12 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-09-03 10:22:23</t>
+          <t>2026-09-03 10:37:46</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2026-09-03 10:22:23</t>
+          <t>2026-09-03 10:37:46</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2697,7 +2697,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ed5fb3e8729c51f1f6e0</t>
+          <t>19e3e56fbdbb764863b6</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2722,7 +2722,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5857251116?se=JBFwTYGn8RGYPeNUtjqvZg&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=08120470A120A602552281268EC24E0672DD8DC2</t>
+          <t>https://www.adzuna.in/land/ad/5857251116?se=fBopXoOn8RGYPeNUtjqvZg&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=08120470A120A602552281268EC24E0672DD8DC2</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2732,12 +2732,12 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-09-03 10:22:23</t>
+          <t>2026-09-03 10:37:46</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2026-09-03 10:22:23</t>
+          <t>2026-09-03 10:37:46</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2026-09-03 10:22:23</t>
+          <t>2026-09-03 10:37:46</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2879,7 +2879,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2026-09-03 10:22:23</t>
+          <t>2026-09-03 10:37:46</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2950,7 +2950,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>2026-09-03 10:22:23</t>
+          <t>2026-09-03 10:37:46</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2026-09-03 10:22:23</t>
+          <t>2026-09-03 10:37:46</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -3052,17 +3052,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>7a992b3096cd6b6cff75</t>
+          <t>f79d2d376b251b5036aa</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Sophos</t>
+          <t>SaidGig</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Full-Stack Software Engineer, India</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>&amp;nbsp;...What You Will Do  We are looking for a highly motivated Full Stack &lt;b&gt;Software Engineer &lt;/b&gt;to join our engineering team and contribute to the development of next-generation web applications, UI frameworks, and developer platforms. The ideal candidate should have strong experience...&amp;nbsp;</t>
+          <t>&amp;nbsp;...Role Overview  Build and stress-test production &lt;b&gt;software &lt;/b&gt;that brings frontier large language models into real applications before release. You will work directly with an &lt;b&gt;engineering &lt;/b&gt;manager on fast-moving generative AI projects, ramp up quickly, and contribute working...&amp;nbsp;</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://jooble.org/desc/-8600884274414448039?ckey=software+engineer&amp;rgn=55126&amp;pos=1&amp;groupId=1087&amp;elckey=105240119481636758&amp;p=1&amp;aq=2553300083316208136&amp;cid=18943&amp;jobAge=877&amp;brelb=100&amp;bscr=69.94773&amp;scr=69.94773</t>
+          <t>https://jooble.org/away/-4293671604513188386?p=1&amp;pos=1&amp;rgn=55126&amp;cid=18943&amp;ckey=software+engineer&amp;jobAge=556&amp;brelb=15&amp;scr=143.80551&amp;bscr=143.80551&amp;aq=-8847622166188189802&amp;elckey=-7972890993014771997</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -3087,17 +3087,17 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-09-03 10:22:23</t>
+          <t>2026-09-03 10:37:46</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2026-09-03 10:22:23</t>
+          <t>2026-09-03 10:37:46</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>345a1a1939d28110d6c0</t>
+          <t>96b20e55f4c7bfdd2bfa</t>
         </is>
       </c>
       <c r="K38" t="n">
@@ -3123,7 +3123,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>9bb0dca389ea44d98e71</t>
+          <t>d67abb6cdfaa555ee8de</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3143,12 +3143,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>What You Will Do We are looking for a highly motivated Full Stack &lt;b&gt;Software Engineer &lt;/b&gt;to join our engineering team and contribute to the development of next-generation web applications, UI frameworks, and developer platforms. The ideal candidate should have strong experience...&amp;nbsp;</t>
+          <t>&amp;nbsp;...What You Will Do  We are looking for a highly motivated Full Stack &lt;b&gt;Software Engineer &lt;/b&gt;to join our engineering team and contribute to the development of next-generation web applications, UI frameworks, and developer platforms. The ideal candidate should have strong experience...&amp;nbsp;</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>https://jooble.org/desc/-2581940985949324908?ckey=software+engineer&amp;rgn=55126&amp;pos=2&amp;groupId=1087&amp;elckey=105240119481636758&amp;p=1&amp;aq=2553300083316208136&amp;cid=18943&amp;jobAge=692&amp;brelb=100&amp;bscr=69.557594&amp;scr=69.557594</t>
+          <t>https://jooble.org/desc/-796507398843211532?ckey=software+engineer&amp;rgn=55126&amp;pos=2&amp;groupId=1087&amp;elckey=-7972890993014771997&amp;p=1&amp;aq=-8847622166188189802&amp;cid=18943&amp;jobAge=892&amp;brelb=15&amp;bscr=143.40276&amp;scr=143.40276</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -3158,17 +3158,17 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-09-03 10:22:23</t>
+          <t>2026-09-03 10:37:46</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2026-09-03 10:22:23</t>
+          <t>2026-09-03 10:37:46</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>d502586cd9be426764f5</t>
+          <t>345a1a1939d28110d6c0</t>
         </is>
       </c>
       <c r="K39" t="n">
@@ -3194,17 +3194,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>304cc450df23115e8f6d</t>
+          <t>c078e64fcf6359061290</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>dscout</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Engineer I</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -3214,12 +3214,14 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>&amp;nbsp;...Building AI-native products is a different problem than building deterministic &lt;b&gt;software:&lt;/b&gt; the same input won't always produce the same output. Good product &lt;b&gt;engineering &lt;/b&gt;here means designing experiences that stay useful, trustworthy, and easy to understand even when the AI...&amp;nbs</t>
+          <t>&amp;nbsp;...set of products and services that help people, businesses and governments realize their greatest potential.  Title and Summary  &lt;b&gt;Software Engineer &lt;/b&gt;I 
+ Who is Mastercard? 
+ Mastercard is a global technology company in the payments industry. Our mission is to connect and...&amp;nbsp;</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://jooble.org/desc/7131857314022588732?ckey=software+engineer&amp;rgn=55126&amp;pos=6&amp;groupId=1087&amp;elckey=105240119481636758&amp;p=1&amp;aq=2553300083316208136&amp;cid=18943&amp;jobAge=290&amp;brelb=100&amp;bscr=47.837234&amp;scr=47.837234</t>
+          <t>https://jooble.org/desc/7995986347102170187?ckey=software+engineer&amp;rgn=55126&amp;pos=4&amp;groupId=1087&amp;elckey=-7972890993014771997&amp;p=1&amp;aq=-8847622166188189802&amp;cid=18943&amp;jobAge=388&amp;brelb=15&amp;bscr=99.29756&amp;scr=99.29756</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -3229,17 +3231,17 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-09-03 10:22:23</t>
+          <t>2026-09-03 10:37:46</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2026-09-03 10:22:23</t>
+          <t>2026-09-03 10:37:46</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>b6c492cc480a7d5849df</t>
+          <t>b9acbee7d077854d07e3</t>
         </is>
       </c>
       <c r="K40" t="n">
@@ -3265,17 +3267,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>209c3e9e07b143bc400b</t>
+          <t>5def1420e8e0020261ba</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Bugcrowd</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Software Engineer - Mayhem Engineering</t>
+          <t>Software engineer</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -3285,12 +3287,14 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>&amp;nbsp;...Job Summary  We are looking for a detail-oriented and analytical &lt;b&gt;Software Engineer &lt;/b&gt;to join our Mayhem Engineering team. In this role, you will be responsible for the design and development of our cloud native, API-first platform for Mayhem, our autonomous application security...&amp;nbsp</t>
+          <t>&amp;nbsp;...set of products and services that help people, businesses and governments realize their greatest potential.  Title and Summary  &lt;b&gt;Software engineer &lt;/b&gt;
+ Overview 
+ This role operates within a globally distributed delivery model, partnering closely with established onshore...&amp;nbsp;</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>https://jooble.org/desc/5156860605023538598?ckey=software+engineer&amp;rgn=55126&amp;pos=9&amp;groupId=1087&amp;elckey=105240119481636758&amp;p=1&amp;aq=2553300083316208136&amp;cid=18943&amp;jobAge=998&amp;brelb=100&amp;bscr=46.09294&amp;scr=46.09294</t>
+          <t>https://jooble.org/away/2894123168819324865?p=1&amp;pos=9&amp;rgn=55126&amp;cid=18943&amp;ckey=software+engineer&amp;jobAge=388&amp;brelb=15&amp;scr=98.79166&amp;bscr=98.79166&amp;aq=-8847622166188189802&amp;elckey=-7972890993014771997</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -3300,17 +3304,17 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-09-03 10:22:23</t>
+          <t>2026-09-03 10:37:46</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2026-09-03 10:22:23</t>
+          <t>2026-09-03 10:37:46</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>b0697f4bd6426d8ace73</t>
+          <t>40ba657d8dba95abbba8</t>
         </is>
       </c>
       <c r="K41" t="n">
@@ -3336,73 +3340,290 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>401485cd05e0c5bb3a49</t>
+          <t>17cf55313d5ea247f8e5</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
+          <t>dscout</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>&amp;nbsp;...Building AI-native products is a different problem than building deterministic &lt;b&gt;software:&lt;/b&gt; the same input won't always produce the same output. Good product &lt;b&gt;engineering &lt;/b&gt;here means designing experiences that stay useful, trustworthy, and easy to understand even when the AI...&amp;nbs</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>https://jooble.org/desc/9161242534232820748?ckey=software+engineer&amp;rgn=55126&amp;pos=11&amp;groupId=1087&amp;elckey=-7972890993014771997&amp;p=1&amp;aq=-8847622166188189802&amp;cid=18943&amp;jobAge=292&amp;brelb=15&amp;bscr=98.559975&amp;scr=98.559975</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>jooble</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>2026-09-03 10:37:46</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2026-09-03 10:37:46</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>b6c492cc480a7d5849df</t>
+        </is>
+      </c>
+      <c r="K42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>no specific skill keywords matched (still passed role/location/experience filters)</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>e5d685c65a2e6a0f005e</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
           <t>Bugcrowd</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>Software Engineer - Mayhem Engineering</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Job Summary We are looking for a detail-oriented and analytical &lt;b&gt;Software Engineer &lt;/b&gt;to join our Mayhem Engineering team. In this role, you will be responsible for the design and development of our cloud native, API-first platform for Mayhem, our autonomous application security...&amp;nbsp;</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>https://jooble.org/desc/-900506412677361858?ckey=software+engineer&amp;rgn=55126&amp;pos=10&amp;groupId=1087&amp;elckey=105240119481636758&amp;p=1&amp;aq=2553300083316208136&amp;cid=18943&amp;jobAge=692&amp;brelb=100&amp;bscr=46.083054&amp;scr=46.083054</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>&amp;nbsp;...Job Summary  We are looking for a detail-oriented and analytical &lt;b&gt;Software Engineer &lt;/b&gt;to join our Mayhem Engineering team. In this role, you will be responsible for the design and development of our cloud native, API-first platform for Mayhem, our autonomous application security...&amp;nbsp</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>https://jooble.org/away/-7118131228584181828?p=1&amp;pos=12&amp;rgn=55126&amp;cid=18943&amp;ckey=software+engineer&amp;jobAge=700&amp;brelb=15&amp;scr=95.443954&amp;bscr=95.443954&amp;aq=-8847622166188189802&amp;elckey=-7972890993014771997</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
         <is>
           <t>jooble</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>2026-09-03 10:22:23</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>2026-09-03 10:22:23</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>367c1ea80677d771c8c6</t>
-        </is>
-      </c>
-      <c r="K42" t="n">
-        <v>0</v>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>no specific skill keywords matched (still passed role/location/experience filters)</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O42" t="inlineStr"/>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>2026-09-03 10:37:46</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2026-09-03 10:37:46</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>b0697f4bd6426d8ace73</t>
+        </is>
+      </c>
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>no specific skill keywords matched (still passed role/location/experience filters)</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>b52deb7d9e67164d9eb0</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Paxos</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Data Platform Engineer</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>&amp;nbsp;...Mastercard and Interactive Brokers. 
+ About the team  The Data &lt;b&gt;Engineering &lt;/b&gt;team at Paxos builds and maintains the data infrastructure...&amp;nbsp;&amp;nbsp;...operational efficiencies. By continuously enhancing our data &lt;b&gt;platform,&lt;/b&gt; we drive innovation, optimize costs, and unlock new re</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>https://jooble.org/away/-7539382523141682190?p=1&amp;pos=7&amp;rgn=55126&amp;cid=18943&amp;ckey=platform+engineer&amp;jobAge=388&amp;brelb=15&amp;scr=43.489666&amp;bscr=43.489666&amp;aq=509908459678714841&amp;elckey=-7100098731825831898</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>jooble</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>2026-09-03 10:37:46</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2026-09-03 10:37:46</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>dd1cf4f3b8d9944df197</t>
+        </is>
+      </c>
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>no specific skill keywords matched (still passed role/location/experience filters)</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>9a689d53aa9287d47d97</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Mastercard</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Site Reliability Engineer I</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>&amp;nbsp;...their greatest potential.  Title and Summary  Site Reliability &lt;b&gt;Engineer &lt;/b&gt;I 
+ Job Description Summary 
+ Job Title 
+ Site Reliability Engineer...&amp;nbsp;&amp;nbsp;...Operations SRE, we are responsible for ensuring that our &lt;b&gt;platform &lt;/b&gt;is stable and healthy. We break down barriers to ru</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>https://jooble.org/desc/5898814598423247422?ckey=platform+engineer&amp;rgn=55126&amp;pos=14&amp;groupId=44066&amp;elckey=-7100098731825831898&amp;p=1&amp;aq=509908459678714841&amp;cid=18943&amp;jobAge=508&amp;brelb=15&amp;bscr=16.641167&amp;scr=16.641167</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>jooble</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>2026-09-03 10:37:46</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>2026-09-03 10:37:46</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>261c2df44dbd387ba937</t>
+        </is>
+      </c>
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>no specific skill keywords matched (still passed role/location/experience filters)</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/vignesh_jobs.xlsx
+++ b/data/vignesh_jobs.xlsx
@@ -496,7 +496,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>210c15cea861a52cfbaf</t>
+          <t>ebde01263946af37d384</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -521,7 +521,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5846723030?se=RJejXYOn8RG378CicPtDfg&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=A12DF7C02E8D43AB5777E0856BEFF63ACAB7EB16</t>
+          <t>https://www.adzuna.in/land/ad/5846723030?se=tJmSO4Wn8RGYPeNUtjqvZg&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=A12DF7C02E8D43AB5777E0856BEFF63ACAB7EB16</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -531,12 +531,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-09-03 10:37:46</t>
+          <t>2026-09-03 10:51:23</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-09-03 10:37:46</t>
+          <t>2026-09-03 10:51:23</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -567,7 +567,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>6b5ea1c172a150f0bc54</t>
+          <t>9a3c552950b1f3ef3f17</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -592,7 +592,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5846723078?se=RJejXYOn8RG378CicPtDfg&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=E4A1A73C5F666ACB84BAE4E1985959AA9FF61296</t>
+          <t>https://www.adzuna.in/land/ad/5846723078?se=tJmSO4Wn8RGYPeNUtjqvZg&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=E4A1A73C5F666ACB84BAE4E1985959AA9FF61296</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -602,12 +602,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-09-03 10:37:46</t>
+          <t>2026-09-03 10:51:23</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-09-03 10:37:46</t>
+          <t>2026-09-03 10:51:23</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -638,7 +638,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>8d4cc96dcbb276bb21da</t>
+          <t>359df8d7b55221cc7a9d</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5846723388?se=RJejXYOn8RG378CicPtDfg&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=43BAAB4C2B9B91025B2C4E2EF1039AF52FAE195C</t>
+          <t>https://www.adzuna.in/land/ad/5846723388?se=tJmSO4Wn8RGYPeNUtjqvZg&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=43BAAB4C2B9B91025B2C4E2EF1039AF52FAE195C</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -673,12 +673,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-09-03 10:37:46</t>
+          <t>2026-09-03 10:51:23</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-09-03 10:37:46</t>
+          <t>2026-09-03 10:51:23</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -709,7 +709,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>08115dabf6d1b27272aa</t>
+          <t>fe6de857dbc303cbb836</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5846723080?se=RJejXYOn8RG378CicPtDfg&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=BDD9C2926EC9D90B80A0CDAE02AC3B622B32FC99</t>
+          <t>https://www.adzuna.in/land/ad/5846723080?se=tJmSO4Wn8RGYPeNUtjqvZg&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=BDD9C2926EC9D90B80A0CDAE02AC3B622B32FC99</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -744,12 +744,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-09-03 10:37:46</t>
+          <t>2026-09-03 10:51:23</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-09-03 10:37:46</t>
+          <t>2026-09-03 10:51:23</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -780,7 +780,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>727041a7e3718f343702</t>
+          <t>61aa861f582979d58f94</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -805,7 +805,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5864426564?se=RJejXYOn8RG378CicPtDfg&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=B290C528C0913CA557D80924BA0AF30FE71A1A00</t>
+          <t>https://www.adzuna.in/land/ad/5864426564?se=tJmSO4Wn8RGYPeNUtjqvZg&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=B290C528C0913CA557D80924BA0AF30FE71A1A00</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-09-03 10:37:46</t>
+          <t>2026-09-03 10:51:23</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-09-03 10:37:46</t>
+          <t>2026-09-03 10:51:23</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -851,7 +851,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>bed86644c34f4c005d35</t>
+          <t>08abf6c4911de258e8c8</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5864426312?se=RJejXYOn8RG378CicPtDfg&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=A27346080A30C3E564878BC09AB7AD3C017DF8A2</t>
+          <t>https://www.adzuna.in/land/ad/5864426312?se=tJmSO4Wn8RGYPeNUtjqvZg&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=A27346080A30C3E564878BC09AB7AD3C017DF8A2</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -886,12 +886,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-09-03 10:37:46</t>
+          <t>2026-09-03 10:51:23</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-09-03 10:37:46</t>
+          <t>2026-09-03 10:51:23</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -922,7 +922,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>e22d57f564e6be323c23</t>
+          <t>b16a668ab1e785cecf6f</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5838614193?se=RJejXYOn8RG378CicPtDfg&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=9A92C6347994E53121C302383944CFFCF637848A</t>
+          <t>https://www.adzuna.in/land/ad/5838614193?se=tJmSO4Wn8RGYPeNUtjqvZg&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=9A92C6347994E53121C302383944CFFCF637848A</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -957,12 +957,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-09-03 10:37:46</t>
+          <t>2026-09-03 10:51:23</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-09-03 10:37:46</t>
+          <t>2026-09-03 10:51:23</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -993,7 +993,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>90ac829e0e0579f886b7</t>
+          <t>a0b6d03eb908896f6064</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5865064890?se=RJejXYOn8RG378CicPtDfg&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=7D08E55F7B8119270271C16BDF7CB0165F3E88A9</t>
+          <t>https://www.adzuna.in/land/ad/5865064890?se=tJmSO4Wn8RGYPeNUtjqvZg&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=7D08E55F7B8119270271C16BDF7CB0165F3E88A9</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-09-03 10:37:46</t>
+          <t>2026-09-03 10:51:23</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-09-03 10:37:46</t>
+          <t>2026-09-03 10:51:23</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1064,7 +1064,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>00836077b2959f1e7824</t>
+          <t>8b5c63763810a68b282f</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5857251208?se=RJejXYOn8RG378CicPtDfg&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=D2EDC0229B026B966CEF760E9377E8C7A3A5D261</t>
+          <t>https://www.adzuna.in/land/ad/5857251208?se=tJmSO4Wn8RGYPeNUtjqvZg&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=D2EDC0229B026B966CEF760E9377E8C7A3A5D261</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1099,12 +1099,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-09-03 10:37:46</t>
+          <t>2026-09-03 10:51:23</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-09-03 10:37:46</t>
+          <t>2026-09-03 10:51:23</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1135,7 +1135,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>57b3b6ad55a818e755a8</t>
+          <t>5a8fdd97e32c2426a986</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5855007034?se=RjrlXYOn8RG374tWD5Donw&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=83A2754BAF8C6CCAD9027F1D5977A1C5CB44300B</t>
+          <t>https://www.adzuna.in/land/ad/5855007034?se=IP3WO4Wn8RGYPeNUtjqvZg&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=83A2754BAF8C6CCAD9027F1D5977A1C5CB44300B</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-09-03 10:37:46</t>
+          <t>2026-09-03 10:51:23</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-09-03 10:37:46</t>
+          <t>2026-09-03 10:51:23</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1206,7 +1206,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>71750aceccf0ed1d2c1b</t>
+          <t>fc2a6f1cc773dd162a26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5855007050?se=RjrlXYOn8RG374tWD5Donw&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=C4EED2A519F03E0B87055D11E8D44FFF3C83C9AE</t>
+          <t>https://www.adzuna.in/land/ad/5855007050?se=IP3WO4Wn8RGYPeNUtjqvZg&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=C4EED2A519F03E0B87055D11E8D44FFF3C83C9AE</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-09-03 10:37:46</t>
+          <t>2026-09-03 10:51:23</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026-09-03 10:37:46</t>
+          <t>2026-09-03 10:51:23</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1277,7 +1277,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>4107de89a1399d76a424</t>
+          <t>aade358b4cd8d976f615</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5855007011?se=RjrlXYOn8RG374tWD5Donw&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=2072E1F6EA4EA104D4C5F33605E51A05D7D97600</t>
+          <t>https://www.adzuna.in/land/ad/5855007011?se=IP3WO4Wn8RGYPeNUtjqvZg&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=2072E1F6EA4EA104D4C5F33605E51A05D7D97600</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1312,12 +1312,12 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-09-03 10:37:46</t>
+          <t>2026-09-03 10:51:23</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026-09-03 10:37:46</t>
+          <t>2026-09-03 10:51:23</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1348,7 +1348,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>c0087f9cf87d470f0815</t>
+          <t>28b08bf14f2b6b04d769</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5837139061?se=RjrlXYOn8RG374tWD5Donw&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=5285674828FE37C646BCC77D46165795A7AC83F3</t>
+          <t>https://www.adzuna.in/land/ad/5837139061?se=IP3WO4Wn8RGYPeNUtjqvZg&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=5285674828FE37C646BCC77D46165795A7AC83F3</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1383,12 +1383,12 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-09-03 10:37:46</t>
+          <t>2026-09-03 10:51:23</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2026-09-03 10:37:46</t>
+          <t>2026-09-03 10:51:23</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1419,7 +1419,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>7d8120415b6fac1d2e9f</t>
+          <t>cccdf0f95ab9827d9fca</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1444,7 +1444,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5857982488?se=RjrlXYOn8RG374tWD5Donw&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=A746E3D6C2072081EB037DB5FF89DB2B1F4A7F7A</t>
+          <t>https://www.adzuna.in/land/ad/5857982488?se=IP3WO4Wn8RGYPeNUtjqvZg&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=A746E3D6C2072081EB037DB5FF89DB2B1F4A7F7A</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-09-03 10:37:46</t>
+          <t>2026-09-03 10:51:23</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2026-09-03 10:37:46</t>
+          <t>2026-09-03 10:51:23</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1490,7 +1490,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>31a99f0e429024e8eaf2</t>
+          <t>faf7ae7a4582822f1584</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1515,7 +1515,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5857982562?se=RjrlXYOn8RG374tWD5Donw&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=D215B0FD12910D6EA0FB670B7E4060E2013251A2</t>
+          <t>https://www.adzuna.in/land/ad/5857982562?se=IP3WO4Wn8RGYPeNUtjqvZg&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=D215B0FD12910D6EA0FB670B7E4060E2013251A2</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1525,12 +1525,12 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-09-03 10:37:46</t>
+          <t>2026-09-03 10:51:23</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2026-09-03 10:37:46</t>
+          <t>2026-09-03 10:51:23</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1561,7 +1561,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>227e67145cbc37e43c64</t>
+          <t>73c2eff3e0719ceb0dc6</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5857251116?se=RjrlXYOn8RG374tWD5Donw&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=08120470A120A602552281268EC24E0672DD8DC2</t>
+          <t>https://www.adzuna.in/land/ad/5857251116?se=IP3WO4Wn8RGYPeNUtjqvZg&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=08120470A120A602552281268EC24E0672DD8DC2</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-09-03 10:37:46</t>
+          <t>2026-09-03 10:51:23</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2026-09-03 10:37:46</t>
+          <t>2026-09-03 10:51:23</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1632,7 +1632,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>3ba20c45590adf90c0a1</t>
+          <t>dfc3fd716d4bc368470d</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1657,7 +1657,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5857251186?se=RjrlXYOn8RG374tWD5Donw&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=86E067A84B4608D56A8DF7DAC543EB1D3E73B398</t>
+          <t>https://www.adzuna.in/land/ad/5857251186?se=IP3WO4Wn8RGYPeNUtjqvZg&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=86E067A84B4608D56A8DF7DAC543EB1D3E73B398</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1667,12 +1667,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-09-03 10:37:46</t>
+          <t>2026-09-03 10:51:23</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2026-09-03 10:37:46</t>
+          <t>2026-09-03 10:51:23</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1703,7 +1703,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>d56d7fc4f8fc3d222e27</t>
+          <t>dea8f6c7e15141eba61e</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5857251152?se=RjrlXYOn8RG374tWD5Donw&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=F6ED6E5761AAB007E2A108EBC1289F6B09295EAC</t>
+          <t>https://www.adzuna.in/land/ad/5857251152?se=IP3WO4Wn8RGYPeNUtjqvZg&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=F6ED6E5761AAB007E2A108EBC1289F6B09295EAC</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1738,12 +1738,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-09-03 10:37:46</t>
+          <t>2026-09-03 10:51:23</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2026-09-03 10:37:46</t>
+          <t>2026-09-03 10:51:23</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1774,7 +1774,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>591ea05c1c1ceb520697</t>
+          <t>aa0d725b507bc2c405cc</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1799,7 +1799,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5837138735?se=RjrlXYOn8RG374tWD5Donw&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=30DB8AF6167416207F9C7D2B1D78CA8ED201388F</t>
+          <t>https://www.adzuna.in/land/ad/5837138735?se=IP3WO4Wn8RGYPeNUtjqvZg&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=30DB8AF6167416207F9C7D2B1D78CA8ED201388F</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-09-03 10:37:46</t>
+          <t>2026-09-03 10:51:23</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2026-09-03 10:37:46</t>
+          <t>2026-09-03 10:51:23</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1845,7 +1845,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ed5c192f469451562a35</t>
+          <t>aed6bcba57d45f6a8118</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1870,7 +1870,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5841509246?se=RjrlXYOn8RG374tWD5Donw&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=77A93A263198B258FF86EBD054D2013BF2EF8C57</t>
+          <t>https://www.adzuna.in/land/ad/5841509246?se=IP3WO4Wn8RGYPeNUtjqvZg&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=77A93A263198B258FF86EBD054D2013BF2EF8C57</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-09-03 10:37:46</t>
+          <t>2026-09-03 10:51:23</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2026-09-03 10:37:46</t>
+          <t>2026-09-03 10:51:23</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2026-09-03 10:37:46</t>
+          <t>2026-09-03 10:51:23</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2027,7 +2027,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2026-09-03 10:37:46</t>
+          <t>2026-09-03 10:51:23</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2098,7 +2098,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2026-09-03 10:37:46</t>
+          <t>2026-09-03 10:51:23</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2169,7 +2169,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2026-09-03 10:37:46</t>
+          <t>2026-09-03 10:51:23</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2240,7 +2240,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2026-09-03 10:37:46</t>
+          <t>2026-09-03 10:51:23</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2311,7 +2311,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2026-09-03 10:37:46</t>
+          <t>2026-09-03 10:51:23</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2026-09-03 10:37:46</t>
+          <t>2026-09-03 10:51:23</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2413,7 +2413,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>6302323b11e6e991b422</t>
+          <t>6002ac2ae8521533e98c</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2438,7 +2438,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5847959683?se=fBopXoOn8RGYPeNUtjqvZg&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=44FCE51978FD48A3291A05FC0AFB8C9CBD5612B2</t>
+          <t>https://www.adzuna.in/land/ad/5847959683?se=Tl8tPIWn8RG374tWD5Donw&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=44FCE51978FD48A3291A05FC0AFB8C9CBD5612B2</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-09-03 10:37:46</t>
+          <t>2026-09-03 10:51:23</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2026-09-03 10:37:46</t>
+          <t>2026-09-03 10:51:23</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2484,7 +2484,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>b7ab0a173036fc899f01</t>
+          <t>146dac94da87a9a72705</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2509,7 +2509,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5854537872?se=fBopXoOn8RGYPeNUtjqvZg&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=71FDDD42F1439DDFA00C96C1342A4501A4014B38</t>
+          <t>https://www.adzuna.in/land/ad/5854537872?se=Tl8tPIWn8RG374tWD5Donw&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=71FDDD42F1439DDFA00C96C1342A4501A4014B38</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-09-03 10:37:46</t>
+          <t>2026-09-03 10:51:23</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2026-09-03 10:37:46</t>
+          <t>2026-09-03 10:51:23</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2555,7 +2555,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>13c12bcdd49faab19e07</t>
+          <t>f7230a1304517a747709</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2580,7 +2580,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5857982562?se=fBopXoOn8RGYPeNUtjqvZg&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=D215B0FD12910D6EA0FB670B7E4060E2013251A2</t>
+          <t>https://www.adzuna.in/land/ad/5857982562?se=Tl8tPIWn8RG374tWD5Donw&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=D215B0FD12910D6EA0FB670B7E4060E2013251A2</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2590,12 +2590,12 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-09-03 10:37:46</t>
+          <t>2026-09-03 10:51:23</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2026-09-03 10:37:46</t>
+          <t>2026-09-03 10:51:23</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2626,7 +2626,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>3ae8ed70dfbd34cb7442</t>
+          <t>2f94a083d73b7468b46a</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2651,7 +2651,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5857982488?se=fBopXoOn8RGYPeNUtjqvZg&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=A746E3D6C2072081EB037DB5FF89DB2B1F4A7F7A</t>
+          <t>https://www.adzuna.in/land/ad/5857982488?se=Tl8tPIWn8RG374tWD5Donw&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=A746E3D6C2072081EB037DB5FF89DB2B1F4A7F7A</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2661,12 +2661,12 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-09-03 10:37:46</t>
+          <t>2026-09-03 10:51:23</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2026-09-03 10:37:46</t>
+          <t>2026-09-03 10:51:23</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2697,7 +2697,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>19e3e56fbdbb764863b6</t>
+          <t>f32a88c653e40cbf47f6</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2722,7 +2722,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5857251116?se=fBopXoOn8RGYPeNUtjqvZg&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=08120470A120A602552281268EC24E0672DD8DC2</t>
+          <t>https://www.adzuna.in/land/ad/5857251116?se=Tl8tPIWn8RG374tWD5Donw&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=08120470A120A602552281268EC24E0672DD8DC2</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2732,12 +2732,12 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-09-03 10:37:46</t>
+          <t>2026-09-03 10:51:23</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2026-09-03 10:37:46</t>
+          <t>2026-09-03 10:51:23</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2026-09-03 10:37:46</t>
+          <t>2026-09-03 10:51:23</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2879,7 +2879,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2026-09-03 10:37:46</t>
+          <t>2026-09-03 10:51:23</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2950,7 +2950,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>2026-09-03 10:37:46</t>
+          <t>2026-09-03 10:51:23</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2026-09-03 10:37:46</t>
+          <t>2026-09-03 10:51:23</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -3052,7 +3052,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>f79d2d376b251b5036aa</t>
+          <t>e31fa26a51d5b645e59b</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://jooble.org/away/-4293671604513188386?p=1&amp;pos=1&amp;rgn=55126&amp;cid=18943&amp;ckey=software+engineer&amp;jobAge=556&amp;brelb=15&amp;scr=143.80551&amp;bscr=143.80551&amp;aq=-8847622166188189802&amp;elckey=-7972890993014771997</t>
+          <t>https://jooble.org/desc/-4293671604513188386?ckey=software+engineer&amp;rgn=55126&amp;pos=1&amp;groupId=1087&amp;elckey=-5682409144298037891&amp;p=1&amp;aq=-5861672892659233616&amp;cid=18943&amp;jobAge=556&amp;brelb=15&amp;bscr=143.64586&amp;scr=143.64586</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-09-03 10:37:46</t>
+          <t>2026-09-03 10:51:23</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2026-09-03 10:37:46</t>
+          <t>2026-09-03 10:51:23</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -3123,7 +3123,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>d67abb6cdfaa555ee8de</t>
+          <t>781ae0f34066f4f0f1fc</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3148,7 +3148,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>https://jooble.org/desc/-796507398843211532?ckey=software+engineer&amp;rgn=55126&amp;pos=2&amp;groupId=1087&amp;elckey=-7972890993014771997&amp;p=1&amp;aq=-8847622166188189802&amp;cid=18943&amp;jobAge=892&amp;brelb=15&amp;bscr=143.40276&amp;scr=143.40276</t>
+          <t>https://jooble.org/desc/-796507398843211532?ckey=software+engineer&amp;rgn=55126&amp;pos=2&amp;groupId=1087&amp;elckey=-5682409144298037891&amp;p=1&amp;aq=-5861672892659233616&amp;cid=18943&amp;jobAge=892&amp;brelb=15&amp;bscr=143.29446&amp;scr=143.29446</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -3158,12 +3158,12 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-09-03 10:37:46</t>
+          <t>2026-09-03 10:51:23</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2026-09-03 10:37:46</t>
+          <t>2026-09-03 10:51:23</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -3194,198 +3194,198 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>c078e64fcf6359061290</t>
+          <t>e545776788065c4ec499</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
+          <t>dscout</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>&amp;nbsp;...Building AI-native products is a different problem than building deterministic &lt;b&gt;software:&lt;/b&gt; the same input won't always produce the same output. Good product &lt;b&gt;engineering &lt;/b&gt;here means designing experiences that stay useful, trustworthy, and easy to understand even when the AI...&amp;nbs</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>https://jooble.org/away/9161242534232820748?p=1&amp;pos=7&amp;rgn=55126&amp;cid=18943&amp;ckey=software+engineer&amp;jobAge=292&amp;brelb=15&amp;scr=99.263084&amp;bscr=99.263084&amp;aq=-5861672892659233616&amp;elckey=-5682409144298037891</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>jooble</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>2026-09-03 10:51:23</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>2026-09-03 10:51:23</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>b6c492cc480a7d5849df</t>
+        </is>
+      </c>
+      <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>no specific skill keywords matched (still passed role/location/experience filters)</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>cfc9cd292d48be218592</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
           <t>Mastercard</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>Software Engineer I</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>&amp;nbsp;...set of products and services that help people, businesses and governments realize their greatest potential.  Title and Summary  &lt;b&gt;Software Engineer &lt;/b&gt;I 
  Who is Mastercard? 
  Mastercard is a global technology company in the payments industry. Our mission is to connect and...&amp;nbsp;</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>https://jooble.org/desc/7995986347102170187?ckey=software+engineer&amp;rgn=55126&amp;pos=4&amp;groupId=1087&amp;elckey=-7972890993014771997&amp;p=1&amp;aq=-8847622166188189802&amp;cid=18943&amp;jobAge=388&amp;brelb=15&amp;bscr=99.29756&amp;scr=99.29756</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>https://jooble.org/desc/7995986347102170187?ckey=software+engineer&amp;rgn=55126&amp;pos=8&amp;groupId=1087&amp;elckey=-5682409144298037891&amp;p=1&amp;aq=-5861672892659233616&amp;cid=18943&amp;jobAge=388&amp;brelb=15&amp;bscr=99.209465&amp;scr=99.209465</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
         <is>
           <t>jooble</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>2026-09-03 10:37:46</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>2026-09-03 10:37:46</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>2026-09-03 10:51:23</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>2026-09-03 10:51:23</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
         <is>
           <t>b9acbee7d077854d07e3</t>
         </is>
       </c>
-      <c r="K40" t="n">
-        <v>0</v>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>no specific skill keywords matched (still passed role/location/experience filters)</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>5def1420e8e0020261ba</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
+      <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>no specific skill keywords matched (still passed role/location/experience filters)</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>bd703a0d36c15aed6967</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
         <is>
           <t>Mastercard</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>Software engineer</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>&amp;nbsp;...set of products and services that help people, businesses and governments realize their greatest potential.  Title and Summary  &lt;b&gt;Software engineer &lt;/b&gt;
  Overview 
  This role operates within a globally distributed delivery model, partnering closely with established onshore...&amp;nbsp;</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>https://jooble.org/away/2894123168819324865?p=1&amp;pos=9&amp;rgn=55126&amp;cid=18943&amp;ckey=software+engineer&amp;jobAge=388&amp;brelb=15&amp;scr=98.79166&amp;bscr=98.79166&amp;aq=-8847622166188189802&amp;elckey=-7972890993014771997</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>https://jooble.org/desc/2894123168819324865?ckey=software+engineer&amp;rgn=55126&amp;pos=9&amp;groupId=1087&amp;elckey=-5682409144298037891&amp;p=1&amp;aq=-5861672892659233616&amp;cid=18943&amp;jobAge=388&amp;brelb=15&amp;bscr=99.17748&amp;scr=99.17748</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
         <is>
           <t>jooble</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>2026-09-03 10:37:46</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>2026-09-03 10:37:46</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>2026-09-03 10:51:23</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2026-09-03 10:51:23</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
         <is>
           <t>40ba657d8dba95abbba8</t>
-        </is>
-      </c>
-      <c r="K41" t="n">
-        <v>0</v>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>no specific skill keywords matched (still passed role/location/experience filters)</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O41" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>17cf55313d5ea247f8e5</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>dscout</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>&amp;nbsp;...Building AI-native products is a different problem than building deterministic &lt;b&gt;software:&lt;/b&gt; the same input won't always produce the same output. Good product &lt;b&gt;engineering &lt;/b&gt;here means designing experiences that stay useful, trustworthy, and easy to understand even when the AI...&amp;nbs</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>https://jooble.org/desc/9161242534232820748?ckey=software+engineer&amp;rgn=55126&amp;pos=11&amp;groupId=1087&amp;elckey=-7972890993014771997&amp;p=1&amp;aq=-8847622166188189802&amp;cid=18943&amp;jobAge=292&amp;brelb=15&amp;bscr=98.559975&amp;scr=98.559975</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>jooble</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>2026-09-03 10:37:46</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>2026-09-03 10:37:46</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>b6c492cc480a7d5849df</t>
         </is>
       </c>
       <c r="K42" t="n">
@@ -3411,7 +3411,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>e5d685c65a2e6a0f005e</t>
+          <t>5be889d2cf406d69876d</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>https://jooble.org/away/-7118131228584181828?p=1&amp;pos=12&amp;rgn=55126&amp;cid=18943&amp;ckey=software+engineer&amp;jobAge=700&amp;brelb=15&amp;scr=95.443954&amp;bscr=95.443954&amp;aq=-8847622166188189802&amp;elckey=-7972890993014771997</t>
+          <t>https://jooble.org/away/-7118131228584181828?p=1&amp;pos=12&amp;rgn=55126&amp;cid=18943&amp;ckey=software+engineer&amp;jobAge=700&amp;brelb=15&amp;scr=95.48117&amp;bscr=95.48117&amp;aq=-5861672892659233616&amp;elckey=-5682409144298037891</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -3446,12 +3446,12 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-09-03 10:37:46</t>
+          <t>2026-09-03 10:51:23</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>2026-09-03 10:37:46</t>
+          <t>2026-09-03 10:51:23</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3482,7 +3482,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>b52deb7d9e67164d9eb0</t>
+          <t>333de30b36160ab3514c</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>https://jooble.org/away/-7539382523141682190?p=1&amp;pos=7&amp;rgn=55126&amp;cid=18943&amp;ckey=platform+engineer&amp;jobAge=388&amp;brelb=15&amp;scr=43.489666&amp;bscr=43.489666&amp;aq=509908459678714841&amp;elckey=-7100098731825831898</t>
+          <t>https://jooble.org/away/-7539382523141682190?p=1&amp;pos=7&amp;rgn=55126&amp;cid=18943&amp;ckey=platform+engineer&amp;jobAge=388&amp;brelb=15&amp;scr=43.42614&amp;bscr=43.42614&amp;aq=-7685922439845799377&amp;elckey=-8542824674986246416</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -3518,12 +3518,12 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-09-03 10:37:46</t>
+          <t>2026-09-03 10:51:23</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>2026-09-03 10:37:46</t>
+          <t>2026-09-03 10:51:23</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3554,7 +3554,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>9a689d53aa9287d47d97</t>
+          <t>43e1b3624f023df85e27</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3582,7 +3582,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>https://jooble.org/desc/5898814598423247422?ckey=platform+engineer&amp;rgn=55126&amp;pos=14&amp;groupId=44066&amp;elckey=-7100098731825831898&amp;p=1&amp;aq=509908459678714841&amp;cid=18943&amp;jobAge=508&amp;brelb=15&amp;bscr=16.641167&amp;scr=16.641167</t>
+          <t>https://jooble.org/away/5898814598423247422?p=1&amp;pos=13&amp;rgn=55126&amp;cid=18943&amp;ckey=platform+engineer&amp;jobAge=508&amp;brelb=15&amp;scr=16.617249&amp;bscr=16.617249&amp;aq=-7685922439845799377&amp;elckey=-8542824674986246416</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -3592,12 +3592,12 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-09-03 10:37:46</t>
+          <t>2026-09-03 10:51:23</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>2026-09-03 10:37:46</t>
+          <t>2026-09-03 10:51:23</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">

--- a/data/vignesh_jobs.xlsx
+++ b/data/vignesh_jobs.xlsx
@@ -536,7 +536,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-09-03 12:42:04</t>
+          <t>2026-09-03 13:22:06</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -607,7 +607,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-09-03 12:42:04</t>
+          <t>2026-09-03 13:22:06</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-09-03 12:42:04</t>
+          <t>2026-09-03 13:22:06</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -749,7 +749,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-09-03 12:42:04</t>
+          <t>2026-09-03 13:22:06</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-09-03 12:42:04</t>
+          <t>2026-09-03 13:22:06</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-09-03 12:42:04</t>
+          <t>2026-09-03 13:22:06</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-09-03 12:42:04</t>
+          <t>2026-09-03 13:22:06</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-09-03 12:42:04</t>
+          <t>2026-09-03 13:22:06</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-09-03 12:42:04</t>
+          <t>2026-09-03 13:22:06</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-09-03 12:42:04</t>
+          <t>2026-09-03 13:22:06</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026-09-03 12:42:04</t>
+          <t>2026-09-03 13:22:06</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026-09-03 12:42:04</t>
+          <t>2026-09-03 13:22:06</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2026-09-03 12:42:04</t>
+          <t>2026-09-03 13:22:06</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2026-09-03 12:42:04</t>
+          <t>2026-09-03 13:22:06</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2026-09-03 12:42:04</t>
+          <t>2026-09-03 13:22:06</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2026-09-03 12:42:04</t>
+          <t>2026-09-03 13:22:06</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2026-09-03 12:42:04</t>
+          <t>2026-09-03 13:22:06</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1743,7 +1743,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2026-09-03 12:42:04</t>
+          <t>2026-09-03 13:22:06</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2026-09-03 12:42:04</t>
+          <t>2026-09-03 13:22:06</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1885,7 +1885,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2026-09-03 12:42:04</t>
+          <t>2026-09-03 13:22:06</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2026-09-03 12:42:04</t>
+          <t>2026-09-03 13:22:06</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2027,7 +2027,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2026-09-03 12:42:04</t>
+          <t>2026-09-03 13:22:06</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2098,7 +2098,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2026-09-03 12:42:04</t>
+          <t>2026-09-03 13:22:06</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2169,7 +2169,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2026-09-03 12:42:04</t>
+          <t>2026-09-03 13:22:06</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2240,7 +2240,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2026-09-03 12:42:04</t>
+          <t>2026-09-03 13:22:06</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2311,7 +2311,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2026-09-03 12:42:04</t>
+          <t>2026-09-03 13:22:06</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2026-09-03 12:42:04</t>
+          <t>2026-09-03 13:22:06</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2413,7 +2413,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>4eb884012ee24b1ca34a</t>
+          <t>05c2acc94d66aec4d217</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://jooble.org/away/6422411571202760777?p=1&amp;pos=2&amp;rgn=55126&amp;cid=18943&amp;ckey=AI+Platform+Engineer&amp;jobAge=702&amp;brelb=15&amp;scr=118.957565&amp;bscr=118.957565&amp;aq=2830692790907888458&amp;elckey=5079428573408986411</t>
+          <t>https://jooble.org/away/6422411571202760777?p=1&amp;pos=4&amp;rgn=55126&amp;cid=18943&amp;ckey=AI+Platform+Engineer&amp;jobAge=703&amp;brelb=15&amp;scr=119.516174&amp;bscr=119.516174&amp;aq=7118800158973352812&amp;elckey=-345446004894194898</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-09-03 12:42:04</t>
+          <t>2026-09-03 13:22:06</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2026-09-03 12:42:04</t>
+          <t>2026-09-03 13:22:06</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2487,25 +2487,99 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>03e68502a71f0a80f489</t>
+          <t>06b47e31d29c102c4473</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
+          <t>SaidGig</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Full-Stack Software Engineer, India</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>&amp;nbsp;...contribute working code early. 
+ Key Responsibilities 
+ Build and deliver full-stack applications, services, and internal tools using &lt;b&gt;Python,&lt;/b&gt; Java, Rust, C#, C++, or TypeScript to exercise model capabilities end to end. 
+ Integrate pre-release model APIs into functional...&amp;nbsp;</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>https://jooble.org/away/-4293671604513188386?p=1&amp;pos=4&amp;rgn=55126&amp;cid=18943&amp;ckey=Python+Developer&amp;jobAge=559&amp;brelb=15&amp;scr=53.35251&amp;bscr=53.35251&amp;aq=2139257649528181899&amp;elckey=8374566165432632815</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>jooble</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>2026-09-03 13:22:06</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2026-09-03 13:22:06</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>4a9ec70bde1620a4856a</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
+        <v>20</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>skill:Python, skill:TypeScript</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>be6d100bdfb7b5a8a76c</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
           <t>Merkle Science</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>Software Engineer(Intern)- Backend</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>&amp;nbsp;...Republic, DCG, Kenetic, GGV and several others. 
  Responsibilities 
@@ -2514,103 +2588,29 @@
  Work with  Redis  for caching, queues, and...&amp;nbsp;</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>https://jooble.org/desc/3479600901415878407?ckey=Python+Developer&amp;rgn=55126&amp;pos=3&amp;groupId=40830&amp;elckey=-4647303329973737492&amp;p=1&amp;aq=-1797048795866796989&amp;cid=18943&amp;jobAge=654&amp;brelb=15&amp;bscr=53.164566&amp;scr=53.164566</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>https://jooble.org/away/3479600901415878407?p=1&amp;pos=5&amp;rgn=55126&amp;cid=18943&amp;ckey=Python+Developer&amp;jobAge=655&amp;brelb=15&amp;scr=53.224674&amp;bscr=53.224674&amp;aq=2139257649528181899&amp;elckey=8374566165432632815</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
         <is>
           <t>jooble</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>2026-09-03 12:42:04</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>2026-09-03 12:42:04</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>2026-09-03 13:22:06</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2026-09-03 13:22:06</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
         <is>
           <t>c88e76ee05d5f22f3af4</t>
-        </is>
-      </c>
-      <c r="K30" t="n">
-        <v>20</v>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>skill:Python, skill:REST APIs</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>631122bca1558b8239fe</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>SaidGig</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Full-Stack Software Engineer, India</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>&amp;nbsp;...contribute working code early. 
- Key Responsibilities 
- Build and deliver full-stack applications, services, and internal tools using &lt;b&gt;Python,&lt;/b&gt; Java, Rust, C#, C++, or TypeScript to exercise model capabilities end to end. 
- Integrate pre-release model APIs into functional...&amp;nbsp;</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>https://jooble.org/away/-4293671604513188386?p=1&amp;pos=4&amp;rgn=55126&amp;cid=18943&amp;ckey=Python+Developer&amp;jobAge=558&amp;brelb=15&amp;scr=53.12955&amp;bscr=53.12955&amp;aq=-1797048795866796989&amp;elckey=-4647303329973737492</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>jooble</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>2026-09-03 12:42:04</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>2026-09-03 12:42:04</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>4a9ec70bde1620a4856a</t>
         </is>
       </c>
       <c r="K31" t="n">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>skill:Python, skill:TypeScript</t>
+          <t>skill:Python, skill:REST APIs</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2636,7 +2636,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>a974714512a8f7869a65</t>
+          <t>99405dc1b6a2ac452cc9</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://jooble.org/away/3479600901415878407?p=1&amp;pos=12&amp;rgn=55126&amp;cid=18943&amp;ckey=Backend+Engineer&amp;jobAge=654&amp;brelb=15&amp;scr=57.927845&amp;bscr=57.927845&amp;aq=3662071841300910996&amp;elckey=556603733564230260</t>
+          <t>https://jooble.org/desc/3479600901415878407?ckey=Backend+Engineer&amp;rgn=55126&amp;pos=8&amp;groupId=41745&amp;elckey=-4868270844738951049&amp;p=1&amp;aq=-1939660106823248520&amp;cid=18943&amp;jobAge=655&amp;brelb=15&amp;bscr=57.969448&amp;scr=57.969448</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2676,12 +2676,12 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-09-03 12:42:04</t>
+          <t>2026-09-03 13:22:06</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2026-09-03 12:42:04</t>
+          <t>2026-09-03 13:22:06</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2712,7 +2712,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>a09519872a3070cfb533</t>
+          <t>b2dfe87abc83a5e3ef5b</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2740,7 +2740,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://jooble.org/desc/6422411571202760777?ckey=Cloud+Platform+Engineer&amp;rgn=55126&amp;pos=18&amp;groupId=1228184036&amp;elckey=4033731776476279844&amp;p=1&amp;aq=2502693114359913515&amp;cid=18943&amp;jobAge=702&amp;brelb=15&amp;bscr=69.76678&amp;scr=69.76678</t>
+          <t>https://jooble.org/away/6422411571202760777?p=1&amp;pos=17&amp;rgn=55126&amp;cid=18943&amp;ckey=Cloud+Platform+Engineer&amp;jobAge=703&amp;brelb=15&amp;scr=69.91147&amp;bscr=69.91147&amp;aq=4898225249629288738&amp;elckey=-1391142801826901465</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-09-03 12:42:04</t>
+          <t>2026-09-03 13:22:06</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2026-09-03 12:42:04</t>
+          <t>2026-09-03 13:22:06</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">

--- a/data/vignesh_jobs.xlsx
+++ b/data/vignesh_jobs.xlsx
@@ -536,7 +536,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-09-03 13:22:06</t>
+          <t>2026-09-03 14:45:24</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -607,7 +607,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-09-03 13:22:06</t>
+          <t>2026-09-03 14:45:24</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-09-03 13:22:06</t>
+          <t>2026-09-03 14:45:24</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -749,7 +749,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-09-03 13:22:06</t>
+          <t>2026-09-03 14:45:24</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-09-03 13:22:06</t>
+          <t>2026-09-03 14:45:24</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-09-03 13:22:06</t>
+          <t>2026-09-03 14:45:24</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-09-03 13:22:06</t>
+          <t>2026-09-03 14:45:24</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-09-03 13:22:06</t>
+          <t>2026-09-03 14:45:24</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-09-03 13:22:06</t>
+          <t>2026-09-03 14:45:24</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-09-03 13:22:06</t>
+          <t>2026-09-03 14:45:24</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026-09-03 13:22:06</t>
+          <t>2026-09-03 14:45:24</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026-09-03 13:22:06</t>
+          <t>2026-09-03 14:45:24</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2026-09-03 13:22:06</t>
+          <t>2026-09-03 14:45:24</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2026-09-03 13:22:06</t>
+          <t>2026-09-03 14:45:24</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2026-09-03 13:22:06</t>
+          <t>2026-09-03 14:45:24</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2026-09-03 13:22:06</t>
+          <t>2026-09-03 14:45:24</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2026-09-03 13:22:06</t>
+          <t>2026-09-03 14:45:24</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1743,7 +1743,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2026-09-03 13:22:06</t>
+          <t>2026-09-03 14:45:24</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2026-09-03 13:22:06</t>
+          <t>2026-09-03 14:45:24</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1885,7 +1885,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2026-09-03 13:22:06</t>
+          <t>2026-09-03 14:45:24</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2026-09-03 13:22:06</t>
+          <t>2026-09-03 14:45:24</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2027,7 +2027,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2026-09-03 13:22:06</t>
+          <t>2026-09-03 14:45:24</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2098,7 +2098,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2026-09-03 13:22:06</t>
+          <t>2026-09-03 14:45:24</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2169,7 +2169,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2026-09-03 13:22:06</t>
+          <t>2026-09-03 14:45:24</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2240,7 +2240,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2026-09-03 13:22:06</t>
+          <t>2026-09-03 14:45:24</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2311,7 +2311,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2026-09-03 13:22:06</t>
+          <t>2026-09-03 14:45:24</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2026-09-03 13:22:06</t>
+          <t>2026-09-03 14:45:24</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2413,7 +2413,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>05c2acc94d66aec4d217</t>
+          <t>b0c1172c99ce7961497b</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://jooble.org/away/6422411571202760777?p=1&amp;pos=4&amp;rgn=55126&amp;cid=18943&amp;ckey=AI+Platform+Engineer&amp;jobAge=703&amp;brelb=15&amp;scr=119.516174&amp;bscr=119.516174&amp;aq=7118800158973352812&amp;elckey=-345446004894194898</t>
+          <t>https://jooble.org/away/6422411571202760777?p=1&amp;pos=4&amp;rgn=55126&amp;cid=18943&amp;ckey=AI+Platform+Engineer&amp;jobAge=704&amp;brelb=15&amp;scr=118.42982&amp;bscr=118.42982&amp;aq=138928839635258681&amp;elckey=-1189356885763907995</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-09-03 13:22:06</t>
+          <t>2026-09-03 14:45:24</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2026-09-03 13:22:06</t>
+          <t>2026-09-03 14:45:24</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2487,17 +2487,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>06b47e31d29c102c4473</t>
+          <t>403378ce5e99941cb5f2</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SaidGig</t>
+          <t>Merkle Science</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Full-Stack Software Engineer, India</t>
+          <t>Software Engineer(Intern)- Backend</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2506,80 +2506,6 @@
         </is>
       </c>
       <c r="E30" t="inlineStr">
-        <is>
-          <t>&amp;nbsp;...contribute working code early. 
- Key Responsibilities 
- Build and deliver full-stack applications, services, and internal tools using &lt;b&gt;Python,&lt;/b&gt; Java, Rust, C#, C++, or TypeScript to exercise model capabilities end to end. 
- Integrate pre-release model APIs into functional...&amp;nbsp;</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>https://jooble.org/away/-4293671604513188386?p=1&amp;pos=4&amp;rgn=55126&amp;cid=18943&amp;ckey=Python+Developer&amp;jobAge=559&amp;brelb=15&amp;scr=53.35251&amp;bscr=53.35251&amp;aq=2139257649528181899&amp;elckey=8374566165432632815</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>jooble</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>2026-09-03 13:22:06</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>2026-09-03 13:22:06</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>4a9ec70bde1620a4856a</t>
-        </is>
-      </c>
-      <c r="K30" t="n">
-        <v>20</v>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>skill:Python, skill:TypeScript</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>be6d100bdfb7b5a8a76c</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Merkle Science</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Software Engineer(Intern)- Backend</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
         <is>
           <t>&amp;nbsp;...Republic, DCG, Kenetic, GGV and several others. 
  Responsibilities 
@@ -2588,9 +2514,83 @@
  Work with  Redis  for caching, queues, and...&amp;nbsp;</t>
         </is>
       </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>https://jooble.org/away/3479600901415878407?p=1&amp;pos=4&amp;rgn=55126&amp;cid=18943&amp;ckey=Python+Developer&amp;jobAge=656&amp;brelb=15&amp;scr=52.80803&amp;bscr=52.80803&amp;aq=1376614371905138334&amp;elckey=7530655284562919718</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>jooble</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>2026-09-03 14:45:24</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2026-09-03 14:45:24</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>c88e76ee05d5f22f3af4</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
+        <v>20</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>skill:Python, skill:REST APIs</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>540043e43283d88f7991</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>SaidGig</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Full-Stack Software Engineer, India</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>&amp;nbsp;...contribute working code early. 
+ Key Responsibilities 
+ Build and deliver full-stack applications, services, and internal tools using &lt;b&gt;Python,&lt;/b&gt; Java, Rust, C#, C++, or TypeScript to exercise model capabilities end to end. 
+ Integrate pre-release model APIs into functional...&amp;nbsp;</t>
+        </is>
+      </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://jooble.org/away/3479600901415878407?p=1&amp;pos=5&amp;rgn=55126&amp;cid=18943&amp;ckey=Python+Developer&amp;jobAge=655&amp;brelb=15&amp;scr=53.224674&amp;bscr=53.224674&amp;aq=2139257649528181899&amp;elckey=8374566165432632815</t>
+          <t>https://jooble.org/away/-4293671604513188386?p=1&amp;pos=5&amp;rgn=55126&amp;cid=18943&amp;ckey=Python+Developer&amp;jobAge=560&amp;brelb=15&amp;scr=52.80085&amp;bscr=52.80085&amp;aq=1376614371905138334&amp;elckey=7530655284562919718</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2600,17 +2600,17 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-09-03 13:22:06</t>
+          <t>2026-09-03 14:45:24</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2026-09-03 13:22:06</t>
+          <t>2026-09-03 14:45:24</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>c88e76ee05d5f22f3af4</t>
+          <t>4a9ec70bde1620a4856a</t>
         </is>
       </c>
       <c r="K31" t="n">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>skill:Python, skill:REST APIs</t>
+          <t>skill:Python, skill:TypeScript</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2636,7 +2636,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>99405dc1b6a2ac452cc9</t>
+          <t>d3d8557d50d5a3fa3ee1</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://jooble.org/desc/3479600901415878407?ckey=Backend+Engineer&amp;rgn=55126&amp;pos=8&amp;groupId=41745&amp;elckey=-4868270844738951049&amp;p=1&amp;aq=-1939660106823248520&amp;cid=18943&amp;jobAge=655&amp;brelb=15&amp;bscr=57.969448&amp;scr=57.969448</t>
+          <t>https://jooble.org/away/3479600901415878407?p=1&amp;pos=8&amp;rgn=55126&amp;cid=18943&amp;ckey=Backend+Engineer&amp;jobAge=656&amp;brelb=15&amp;scr=57.430958&amp;bscr=57.430958&amp;aq=-6990000238022384582&amp;elckey=-5712181725608664146</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2676,12 +2676,12 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-09-03 13:22:06</t>
+          <t>2026-09-03 14:45:24</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2026-09-03 13:22:06</t>
+          <t>2026-09-03 14:45:24</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2712,7 +2712,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>b2dfe87abc83a5e3ef5b</t>
+          <t>8da5afd653edbaa7daef</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2740,7 +2740,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://jooble.org/away/6422411571202760777?p=1&amp;pos=17&amp;rgn=55126&amp;cid=18943&amp;ckey=Cloud+Platform+Engineer&amp;jobAge=703&amp;brelb=15&amp;scr=69.91147&amp;bscr=69.91147&amp;aq=4898225249629288738&amp;elckey=-1391142801826901465</t>
+          <t>https://jooble.org/desc/6422411571202760777?ckey=Cloud+Platform+Engineer&amp;rgn=55126&amp;pos=17&amp;groupId=1228184036&amp;elckey=-2235053682696614562&amp;p=1&amp;aq=7339162732039312294&amp;cid=18943&amp;jobAge=704&amp;brelb=15&amp;bscr=70.14097&amp;scr=70.14097</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-09-03 13:22:06</t>
+          <t>2026-09-03 14:45:24</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2026-09-03 13:22:06</t>
+          <t>2026-09-03 14:45:24</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">

--- a/data/vignesh_jobs.xlsx
+++ b/data/vignesh_jobs.xlsx
@@ -536,7 +536,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-09-03 14:45:24</t>
+          <t>2026-09-03 16:33:17</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -607,7 +607,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-09-03 14:45:24</t>
+          <t>2026-09-03 16:33:17</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-09-03 14:45:24</t>
+          <t>2026-09-03 16:33:17</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -749,7 +749,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-09-03 14:45:24</t>
+          <t>2026-09-03 16:33:17</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-09-03 14:45:24</t>
+          <t>2026-09-03 16:33:17</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-09-03 14:45:24</t>
+          <t>2026-09-03 16:33:17</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-09-03 14:45:24</t>
+          <t>2026-09-03 16:33:17</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-09-03 14:45:24</t>
+          <t>2026-09-03 16:33:17</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-09-03 14:45:24</t>
+          <t>2026-09-03 16:33:17</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-09-03 14:45:24</t>
+          <t>2026-09-03 16:33:17</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026-09-03 14:45:24</t>
+          <t>2026-09-03 16:33:17</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026-09-03 14:45:24</t>
+          <t>2026-09-03 16:33:17</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2026-09-03 14:45:24</t>
+          <t>2026-09-03 16:33:17</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2026-09-03 14:45:24</t>
+          <t>2026-09-03 16:33:17</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2026-09-03 14:45:24</t>
+          <t>2026-09-03 16:33:17</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2026-09-03 14:45:24</t>
+          <t>2026-09-03 16:33:17</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2026-09-03 14:45:24</t>
+          <t>2026-09-03 16:33:17</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1743,7 +1743,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2026-09-03 14:45:24</t>
+          <t>2026-09-03 16:33:17</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2026-09-03 14:45:24</t>
+          <t>2026-09-03 16:33:17</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1885,7 +1885,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2026-09-03 14:45:24</t>
+          <t>2026-09-03 16:33:17</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2026-09-03 14:45:24</t>
+          <t>2026-09-03 16:33:17</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2027,7 +2027,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2026-09-03 14:45:24</t>
+          <t>2026-09-03 16:33:17</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2098,7 +2098,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2026-09-03 14:45:24</t>
+          <t>2026-09-03 16:33:17</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2169,7 +2169,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2026-09-03 14:45:24</t>
+          <t>2026-09-03 16:33:17</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2240,7 +2240,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2026-09-03 14:45:24</t>
+          <t>2026-09-03 16:33:17</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2311,7 +2311,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2026-09-03 14:45:24</t>
+          <t>2026-09-03 16:33:17</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2026-09-03 14:45:24</t>
+          <t>2026-09-03 16:33:17</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2413,7 +2413,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>b0c1172c99ce7961497b</t>
+          <t>fe45362fad0de244456d</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://jooble.org/away/6422411571202760777?p=1&amp;pos=4&amp;rgn=55126&amp;cid=18943&amp;ckey=AI+Platform+Engineer&amp;jobAge=704&amp;brelb=15&amp;scr=118.42982&amp;bscr=118.42982&amp;aq=138928839635258681&amp;elckey=-1189356885763907995</t>
+          <t>https://jooble.org/desc/6422411571202760777?ckey=AI+Platform+Engineer&amp;rgn=55126&amp;pos=1&amp;groupId=1793437986&amp;elckey=1237290797552541013&amp;p=1&amp;aq=-7610482737836464938&amp;cid=18943&amp;jobAge=706&amp;brelb=15&amp;bscr=117.564804&amp;scr=117.564804</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-09-03 14:45:24</t>
+          <t>2026-09-03 16:33:17</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2026-09-03 14:45:24</t>
+          <t>2026-09-03 16:33:17</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2487,25 +2487,99 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>403378ce5e99941cb5f2</t>
+          <t>f84b5cdf7da4ec346dae</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
+          <t>SaidGig</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Full-Stack Software Engineer, India</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>&amp;nbsp;...contribute working code early. 
+ Key Responsibilities 
+ Build and deliver full-stack applications, services, and internal tools using &lt;b&gt;Python,&lt;/b&gt; Java, Rust, C#, C++, or TypeScript to exercise model capabilities end to end. 
+ Integrate pre-release model APIs into functional...&amp;nbsp;</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>https://jooble.org/away/-4293671604513188386?p=1&amp;pos=3&amp;rgn=55126&amp;cid=18943&amp;ckey=Python+Developer&amp;jobAge=562&amp;brelb=15&amp;scr=52.45933&amp;bscr=52.45933&amp;aq=7420785423372502193&amp;elckey=-8489441105830182890</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>jooble</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>2026-09-03 16:33:17</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2026-09-03 16:33:17</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>4a9ec70bde1620a4856a</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
+        <v>20</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>skill:Python, skill:TypeScript</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>8cabaf1908a499870002</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
           <t>Merkle Science</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>Software Engineer(Intern)- Backend</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>&amp;nbsp;...Republic, DCG, Kenetic, GGV and several others. 
  Responsibilities 
@@ -2514,103 +2588,29 @@
  Work with  Redis  for caching, queues, and...&amp;nbsp;</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>https://jooble.org/away/3479600901415878407?p=1&amp;pos=4&amp;rgn=55126&amp;cid=18943&amp;ckey=Python+Developer&amp;jobAge=656&amp;brelb=15&amp;scr=52.80803&amp;bscr=52.80803&amp;aq=1376614371905138334&amp;elckey=7530655284562919718</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>https://jooble.org/desc/3479600901415878407?ckey=Python+Developer&amp;rgn=55126&amp;pos=5&amp;groupId=40830&amp;elckey=-8489441105830182890&amp;p=1&amp;aq=7420785423372502193&amp;cid=18943&amp;jobAge=658&amp;brelb=15&amp;bscr=52.072277&amp;scr=52.072277</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
         <is>
           <t>jooble</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>2026-09-03 14:45:24</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>2026-09-03 14:45:24</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>2026-09-03 16:33:17</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2026-09-03 16:33:17</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
         <is>
           <t>c88e76ee05d5f22f3af4</t>
-        </is>
-      </c>
-      <c r="K30" t="n">
-        <v>20</v>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>skill:Python, skill:REST APIs</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>540043e43283d88f7991</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>SaidGig</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Full-Stack Software Engineer, India</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>&amp;nbsp;...contribute working code early. 
- Key Responsibilities 
- Build and deliver full-stack applications, services, and internal tools using &lt;b&gt;Python,&lt;/b&gt; Java, Rust, C#, C++, or TypeScript to exercise model capabilities end to end. 
- Integrate pre-release model APIs into functional...&amp;nbsp;</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>https://jooble.org/away/-4293671604513188386?p=1&amp;pos=5&amp;rgn=55126&amp;cid=18943&amp;ckey=Python+Developer&amp;jobAge=560&amp;brelb=15&amp;scr=52.80085&amp;bscr=52.80085&amp;aq=1376614371905138334&amp;elckey=7530655284562919718</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>jooble</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>2026-09-03 14:45:24</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>2026-09-03 14:45:24</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>4a9ec70bde1620a4856a</t>
         </is>
       </c>
       <c r="K31" t="n">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>skill:Python, skill:TypeScript</t>
+          <t>skill:Python, skill:REST APIs</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2636,7 +2636,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>d3d8557d50d5a3fa3ee1</t>
+          <t>a5a97d044631a5032a2d</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://jooble.org/away/3479600901415878407?p=1&amp;pos=8&amp;rgn=55126&amp;cid=18943&amp;ckey=Backend+Engineer&amp;jobAge=656&amp;brelb=15&amp;scr=57.430958&amp;bscr=57.430958&amp;aq=-6990000238022384582&amp;elckey=-5712181725608664146</t>
+          <t>https://jooble.org/desc/3479600901415878407?ckey=Backend+Engineer&amp;rgn=55126&amp;pos=8&amp;groupId=41745&amp;elckey=-3285534042292215138&amp;p=1&amp;aq=531656242354017487&amp;cid=18943&amp;jobAge=658&amp;brelb=15&amp;bscr=56.879696&amp;scr=56.879696</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2676,12 +2676,12 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-09-03 14:45:24</t>
+          <t>2026-09-03 16:33:17</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2026-09-03 14:45:24</t>
+          <t>2026-09-03 16:33:17</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2712,7 +2712,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>8da5afd653edbaa7daef</t>
+          <t>4abbad2faf49987f7f7d</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2740,7 +2740,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://jooble.org/desc/6422411571202760777?ckey=Cloud+Platform+Engineer&amp;rgn=55126&amp;pos=17&amp;groupId=1228184036&amp;elckey=-2235053682696614562&amp;p=1&amp;aq=7339162732039312294&amp;cid=18943&amp;jobAge=704&amp;brelb=15&amp;bscr=70.14097&amp;scr=70.14097</t>
+          <t>https://jooble.org/away/6422411571202760777?p=1&amp;pos=17&amp;rgn=55126&amp;cid=18943&amp;ckey=Cloud+Platform+Engineer&amp;jobAge=706&amp;brelb=15&amp;scr=68.48433&amp;bscr=68.48433&amp;aq=-8505660715143753827&amp;elckey=191594000619834446</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-09-03 14:45:24</t>
+          <t>2026-09-03 16:33:17</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2026-09-03 14:45:24</t>
+          <t>2026-09-03 16:33:17</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">

--- a/data/vignesh_jobs.xlsx
+++ b/data/vignesh_jobs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O33"/>
+  <dimension ref="A1:O32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -536,7 +536,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-09-03 16:33:17</t>
+          <t>2026-09-04 02:30:49</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -607,7 +607,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-09-03 16:33:17</t>
+          <t>2026-09-04 02:30:49</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-09-03 16:33:17</t>
+          <t>2026-09-04 02:30:49</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -749,7 +749,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-09-03 16:33:17</t>
+          <t>2026-09-04 02:30:49</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-09-03 16:33:17</t>
+          <t>2026-09-04 02:30:49</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-09-03 16:33:17</t>
+          <t>2026-09-04 02:30:49</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-09-03 16:33:17</t>
+          <t>2026-09-04 02:30:49</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-09-03 16:33:17</t>
+          <t>2026-09-04 02:30:49</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-09-03 16:33:17</t>
+          <t>2026-09-04 02:30:49</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-09-03 16:33:17</t>
+          <t>2026-09-04 02:30:49</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026-09-03 16:33:17</t>
+          <t>2026-09-04 02:30:49</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026-09-03 16:33:17</t>
+          <t>2026-09-04 02:30:49</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2026-09-03 16:33:17</t>
+          <t>2026-09-04 02:30:49</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2026-09-03 16:33:17</t>
+          <t>2026-09-04 02:30:49</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1490,17 +1490,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>bedebd0e647137fbab9e</t>
+          <t>eef4f69bb6a9c4941d31</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Zorba Consulting India</t>
+          <t>Sollys Consulting and Solutions Pvt Ltd</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Python developer</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1510,12 +1510,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Role Overview We are looking for an experienced Python Developer with strong hands-on expertise in Python coding, Streamlit, Flask, and FastAPI . The candidate will be responsible for developing Python-based services, Streamlit applications, automation scripts, API integrations, and data-processing </t>
+          <t>We are hiring Female for Python Developers with good salary and work environment. Candidate with good communication skills and End to end in python are entertained. Skills:- Django, Flask, MySQL and PostgreSQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/details/5857693060?utm_medium=api&amp;utm_source=447522e9</t>
+          <t>https://www.adzuna.in/details/3532568531?utm_medium=api&amp;utm_source=447522e9</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1530,20 +1530,20 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2026-09-03 16:33:17</t>
+          <t>2026-09-04 02:30:49</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>443a693318c3c6f3b107</t>
+          <t>92421b2ef4abc945af31</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>skill:Python, skill:Flask, skill:SQL</t>
+          <t>skill:Python, skill:Flask</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1561,17 +1561,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>eef4f69bb6a9c4941d31</t>
+          <t>95ef91cebb610fe29e79</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Sollys Consulting and Solutions Pvt Ltd</t>
+          <t>Xoriant Corporation</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Python developer</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>We are hiring Female for Python Developers with good salary and work environment. Candidate with good communication skills and End to end in python are entertained. Skills:- Django, Flask, MySQL and PostgreSQL</t>
+          <t>Role &amp; responsibilities : Development and debugging of applications using Golang or Python. Position Description : Hands-on software development experience in Python or Golang. Strong experience and knowledge of micro services, and distributed systems. Good analytical and debugging skills to root ca</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/details/3532568531?utm_medium=api&amp;utm_source=447522e9</t>
+          <t>https://www.adzuna.in/details/5850370781?utm_medium=api&amp;utm_source=447522e9</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2026-09-03 16:33:17</t>
+          <t>2026-09-04 02:30:49</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>92421b2ef4abc945af31</t>
+          <t>59c377651e2ad74ba9c6</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>skill:Python, skill:Flask</t>
+          <t>skill:Python, skill:Distributed Systems</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1632,12 +1632,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>95ef91cebb610fe29e79</t>
+          <t>78723e7ad5a8abc08a88</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Xoriant Corporation</t>
+          <t>Conneqt Business Solutions Limited</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Role &amp; responsibilities : Development and debugging of applications using Golang or Python. Position Description : Hands-on software development experience in Python or Golang. Strong experience and knowledge of micro services, and distributed systems. Good analytical and debugging skills to root ca</t>
+          <t>Required Skills and Qualifications: • Strong experience in Python for backend development. • Proficiency in MSSQL and writing optimized SQL queries and stored procedures. • Hands-on experience with Redis and Celery for task queues and caching. • Expertise in RabbitMQ for messaging systems. • Practic</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/details/5850370781?utm_medium=api&amp;utm_source=447522e9</t>
+          <t>https://www.adzuna.in/details/5806699867?utm_medium=api&amp;utm_source=447522e9</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1672,20 +1672,20 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2026-09-03 16:33:17</t>
+          <t>2026-09-04 02:30:49</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>59c377651e2ad74ba9c6</t>
+          <t>72e4255119e60b04397d</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>skill:Python, skill:Distributed Systems</t>
+          <t>skill:Python, skill:SQL, skill:Git</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1703,32 +1703,32 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>78723e7ad5a8abc08a88</t>
+          <t>be9947e662597926015b</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Conneqt Business Solutions Limited</t>
+          <t>Trigent Software Private Limited</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Richmond Town, Bangalore</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Required Skills and Qualifications: • Strong experience in Python for backend development. • Proficiency in MSSQL and writing optimized SQL queries and stored procedures. • Hands-on experience with Redis and Celery for task queues and caching. • Expertise in RabbitMQ for messaging systems. • Practic</t>
+          <t>Must-Have Skills Frontend Strong JavaScript fundamentals (ES6, async/await, closures) React experience preferred (hooks, state management, component architecture) Backend Proficient in Python, writing production-grade code Hands-on experience with FastAPI or Flask for building REST APIs Database Exp</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/details/5806699867?utm_medium=api&amp;utm_source=447522e9</t>
+          <t>https://www.adzuna.in/details/5867507549?utm_medium=api&amp;utm_source=447522e9</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1743,20 +1743,20 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2026-09-03 16:33:17</t>
+          <t>2026-09-04 02:30:49</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>72e4255119e60b04397d</t>
+          <t>f5812926dbe4c720e676</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>skill:Python, skill:SQL, skill:Git</t>
+          <t>skill:Python, skill:JavaScript, skill:REST APIs, skill:Flask, skill:SQL</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1774,7 +1774,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>be9947e662597926015b</t>
+          <t>4cabe1a20fc46c23e821</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1799,7 +1799,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/details/5867507549?utm_medium=api&amp;utm_source=447522e9</t>
+          <t>https://www.adzuna.in/details/5867507551?utm_medium=api&amp;utm_source=447522e9</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2026-09-03 16:33:17</t>
+          <t>2026-09-04 02:30:49</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1845,32 +1845,32 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>4cabe1a20fc46c23e821</t>
+          <t>4e011ae5dfc0e54a4b20</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Trigent Software Private Limited</t>
+          <t>Upswing Financial Technologies Private Limited</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Cloud Platform Engineer - DevOps</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Richmond Town, Bangalore</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Must-Have Skills Frontend Strong JavaScript fundamentals (ES6, async/await, closures) React experience preferred (hooks, state management, component architecture) Backend Proficient in Python, writing production-grade code Hands-on experience with FastAPI or Flask for building REST APIs Database Exp</t>
+          <t>As part of the Cloud Platform / Devops team at Upswing, you will get to work on building state-of-the-art infrastructure for the future. You will also be – Building Infrastructure on AWS driven through terraform and building automation tools for deployment, infrastructure management, and observabili</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/details/5867507551?utm_medium=api&amp;utm_source=447522e9</t>
+          <t>https://www.adzuna.in/details/4197215220?utm_medium=api&amp;utm_source=447522e9</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1885,20 +1885,20 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2026-09-03 16:33:17</t>
+          <t>2026-09-04 02:30:49</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>f5812926dbe4c720e676</t>
+          <t>d48015c2d9ffcb41b244</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>skill:Python, skill:JavaScript, skill:REST APIs, skill:Flask, skill:SQL</t>
+          <t>skill:Observability, skill:Kubernetes</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1916,17 +1916,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>4e011ae5dfc0e54a4b20</t>
+          <t>4bec0093790580d3fce3</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Upswing Financial Technologies Private Limited</t>
+          <t>Wissen Technology</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer - DevOps</t>
+          <t>site reliability engineer</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>As part of the Cloud Platform / Devops team at Upswing, you will get to work on building state-of-the-art infrastructure for the future. You will also be – Building Infrastructure on AWS driven through terraform and building automation tools for deployment, infrastructure management, and observabili</t>
+          <t>- Experience comparable to DevOps SIRE providing SME-tevel application or platform support with responsibility for designing and automating operational procedures and best practices -Experience writing python and shell scripts to perform health checks and automations - Experience with Linux System A</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/details/4197215220?utm_medium=api&amp;utm_source=447522e9</t>
+          <t>https://www.adzuna.in/details/5416884005?utm_medium=api&amp;utm_source=447522e9</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2026-09-03 16:33:17</t>
+          <t>2026-09-04 02:30:49</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>d48015c2d9ffcb41b244</t>
+          <t>6c3787d1f113336a39c1</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -1969,7 +1969,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>skill:Observability, skill:Kubernetes</t>
+          <t>skill:Python, skill:Health Checks</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1987,7 +1987,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>4bec0093790580d3fce3</t>
+          <t>f5d403ed720a472c876b</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1997,7 +1997,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>site reliability engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2007,12 +2007,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>- Experience comparable to DevOps SIRE providing SME-tevel application or platform support with responsibility for designing and automating operational procedures and best practices -Experience writing python and shell scripts to perform health checks and automations - Experience with Linux System A</t>
+          <t>2 years of hands-on experience in Java development. Strong knowledge of Boto3/Boto AWS libraries (Python). Solid experience with AWS services: EC2, ELB/ALB, CloudWatch. Familiarity with SRE practices and maintenance processes. Strong experience in debugging, troubleshooting, and unit testing. Profic</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/details/5416884005?utm_medium=api&amp;utm_source=447522e9</t>
+          <t>https://www.adzuna.in/details/5211779025?utm_medium=api&amp;utm_source=447522e9</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2027,20 +2027,20 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2026-09-03 16:33:17</t>
+          <t>2026-09-04 02:30:49</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>6c3787d1f113336a39c1</t>
+          <t>03ea2a71e141f631af37</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>skill:Python, skill:Health Checks</t>
+          <t>skill:Python, skill:Git, skill:Cloud-Native, skill:Distributed Systems</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2058,17 +2058,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>f5d403ed720a472c876b</t>
+          <t>68d177dcd7e961cef2cb</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Wissen Technology</t>
+          <t>Zensar Technologies</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>SRE Engineer</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2078,12 +2078,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2 years of hands-on experience in Java development. Strong knowledge of Boto3/Boto AWS libraries (Python). Solid experience with AWS services: EC2, ELB/ALB, CloudWatch. Familiarity with SRE practices and maintenance processes. Strong experience in debugging, troubleshooting, and unit testing. Profic</t>
+          <t>Description We are seeking a seasoned Site Reliability Engineering to take end-to-end ownership of our retail eCommerce platform's operational excellence. You will drive SRE culture across engineering teams, champion observability, and work with a cross-functional onsite/offshore team to deliver exc</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/details/5211779025?utm_medium=api&amp;utm_source=447522e9</t>
+          <t>https://www.adzuna.in/details/5867254752?utm_medium=api&amp;utm_source=447522e9</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2098,20 +2098,20 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2026-09-03 16:33:17</t>
+          <t>2026-09-04 02:30:49</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>03ea2a71e141f631af37</t>
+          <t>1c13ecdc9e7604a73142</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>skill:Python, skill:Git, skill:Cloud-Native, skill:Distributed Systems</t>
+          <t>skill:Observability, skill:Kubernetes</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2129,12 +2129,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>68d177dcd7e961cef2cb</t>
+          <t>1e8d90b2f7b27eec4aee</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Zensar Technologies</t>
+          <t>Wissen Technology</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Description We are seeking a seasoned Site Reliability Engineering to take end-to-end ownership of our retail eCommerce platform's operational excellence. You will drive SRE culture across engineering teams, champion observability, and work with a cross-functional onsite/offshore team to deliver exc</t>
+          <t>Job Description. 1. Cloud experience (Any cloud is fine although AWS is preferred. If non-AWS cloud, then the experience should reflect familiarity with the cloud's common services) 2. Good grasp of Scripting (in Linux for sure ie bash/sh/zsh etc, Windows : nice to have) 3. Python or Java or JS basi</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/details/5867254752?utm_medium=api&amp;utm_source=447522e9</t>
+          <t>https://www.adzuna.in/details/5501134569?utm_medium=api&amp;utm_source=447522e9</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2169,12 +2169,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2026-09-03 16:33:17</t>
+          <t>2026-09-04 02:30:49</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1c13ecdc9e7604a73142</t>
+          <t>32b60b6a0297c5084f53</t>
         </is>
       </c>
       <c r="K25" t="n">
@@ -2182,7 +2182,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>skill:Observability, skill:Kubernetes</t>
+          <t>skill:Python, skill:Bash</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2200,17 +2200,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1e8d90b2f7b27eec4aee</t>
+          <t>0d112f518f8db899e3c6</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Wissen Technology</t>
+          <t>Jobdost</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>SRE Engineer</t>
+          <t>SRE Devops</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2220,12 +2220,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Job Description. 1. Cloud experience (Any cloud is fine although AWS is preferred. If non-AWS cloud, then the experience should reflect familiarity with the cloud's common services) 2. Good grasp of Scripting (in Linux for sure ie bash/sh/zsh etc, Windows : nice to have) 3. Python or Java or JS basi</t>
+          <t>Candidates MUST HAVE : Experience with Infrastructure-as-Code tools(IaS) like Terraform and Cloud Formation. Proficiency in cloud-native technologies and architectures (Docker/ Kubernetes), Ci/CD pipelines. Good experience in Javascript. Expertise in Linux / Windows environment. Good Experience in S</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/details/5501134569?utm_medium=api&amp;utm_source=447522e9</t>
+          <t>https://www.adzuna.in/details/4344577925?utm_medium=api&amp;utm_source=447522e9</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2240,20 +2240,20 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2026-09-03 16:33:17</t>
+          <t>2026-09-04 02:30:49</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>32b60b6a0297c5084f53</t>
+          <t>08c477bc04ba32062d49</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>skill:Python, skill:Bash</t>
+          <t>skill:Python, skill:JavaScript, skill:Bash, skill:Git, skill:Cloud-Native, skill:Kubernetes</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2271,17 +2271,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0d112f518f8db899e3c6</t>
+          <t>0e6b548516e16807909f</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Jobdost</t>
+          <t>Wissen Technology</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>SRE Devops</t>
+          <t>Devops/ SRE</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2291,12 +2291,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Candidates MUST HAVE : Experience with Infrastructure-as-Code tools(IaS) like Terraform and Cloud Formation. Proficiency in cloud-native technologies and architectures (Docker/ Kubernetes), Ci/CD pipelines. Good experience in Javascript. Expertise in Linux / Windows environment. Good Experience in S</t>
+          <t>The candidate should have a background in development/programming with experience in at least one of the following: .NET, Java (Spring Boot), ReactJS, or AngularJS. Primary Skills: AWS or GCP Cloud DevOps CI/CD pipelines (e.g., Azure DevOps, Jenkins) Python/Bash/PowerShell scripting Secondary Skills</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/details/4344577925?utm_medium=api&amp;utm_source=447522e9</t>
+          <t>https://www.adzuna.in/details/5211779221?utm_medium=api&amp;utm_source=447522e9</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2311,20 +2311,20 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2026-09-03 16:33:17</t>
+          <t>2026-09-04 02:30:49</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>08c477bc04ba32062d49</t>
+          <t>48fe7642ecb269a15f16</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>skill:Python, skill:JavaScript, skill:Bash, skill:Git, skill:Cloud-Native, skill:Kubernetes</t>
+          <t>skill:Python, skill:Bash, skill:Kubernetes</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2342,96 +2342,25 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0e6b548516e16807909f</t>
+          <t>37ef472e64ecfe6212ab</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Wissen Technology</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Devops/ SRE</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>India</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
-        <is>
-          <t>The candidate should have a background in development/programming with experience in at least one of the following: .NET, Java (Spring Boot), ReactJS, or AngularJS. Primary Skills: AWS or GCP Cloud DevOps CI/CD pipelines (e.g., Azure DevOps, Jenkins) Python/Bash/PowerShell scripting Secondary Skills</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>https://www.adzuna.in/details/5211779221?utm_medium=api&amp;utm_source=447522e9</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>adzuna</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>2026-09-03 11:14:10</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2026-09-03 16:33:17</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>48fe7642ecb269a15f16</t>
-        </is>
-      </c>
-      <c r="K28" t="n">
-        <v>30</v>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>skill:Python, skill:Bash, skill:Kubernetes</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>fe45362fad0de244456d</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Mastercard</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>AI Engineer</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
         <is>
           <t>&amp;nbsp;...governments realize their greatest potential.  Title and Summary  &lt;b&gt;AI Engineer &lt;/b&gt;
  Job Description Summary 
@@ -2439,73 +2368,73 @@
 • Develop and maintain scalable AI/ML pipeline</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>https://jooble.org/desc/6422411571202760777?ckey=AI+Platform+Engineer&amp;rgn=55126&amp;pos=1&amp;groupId=1793437986&amp;elckey=1237290797552541013&amp;p=1&amp;aq=-7610482737836464938&amp;cid=18943&amp;jobAge=706&amp;brelb=15&amp;bscr=117.564804&amp;scr=117.564804</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>https://jooble.org/desc/6422411571202760777?ckey=AI+Platform+Engineer&amp;rgn=55126&amp;pos=3&amp;groupId=1793437986&amp;elckey=-2964459282113035987&amp;p=1&amp;aq=185338811351190800&amp;cid=18943&amp;jobAge=716&amp;brelb=15&amp;bscr=117.89957&amp;scr=117.89957</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
         <is>
           <t>jooble</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>2026-09-03 16:33:17</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>2026-09-03 16:33:17</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>2026-09-04 02:30:49</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2026-09-04 02:30:49</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
         <is>
           <t>ff5f93b49b3a3a914f94</t>
         </is>
       </c>
-      <c r="K29" t="n">
+      <c r="K28" t="n">
         <v>20</v>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t>skill:RAG, skill:Agentic AI</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>f84b5cdf7da4ec346dae</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>3ea7622d2452055687f8</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
         <is>
           <t>SaidGig</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>Full-Stack Software Engineer, India</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>&amp;nbsp;...contribute working code early. 
  Key Responsibilities 
@@ -2513,73 +2442,73 @@
  Integrate pre-release model APIs into functional...&amp;nbsp;</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>https://jooble.org/away/-4293671604513188386?p=1&amp;pos=3&amp;rgn=55126&amp;cid=18943&amp;ckey=Python+Developer&amp;jobAge=562&amp;brelb=15&amp;scr=52.45933&amp;bscr=52.45933&amp;aq=7420785423372502193&amp;elckey=-8489441105830182890</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>https://jooble.org/away/-4293671604513188386?p=1&amp;pos=3&amp;rgn=55126&amp;cid=18943&amp;ckey=Python+Developer&amp;jobAge=572&amp;brelb=15&amp;scr=52.713013&amp;bscr=52.713013&amp;aq=-3883215854646545784&amp;elckey=5755552888213791726</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
         <is>
           <t>jooble</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>2026-09-03 16:33:17</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>2026-09-03 16:33:17</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>2026-09-04 02:30:49</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2026-09-04 02:30:49</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
         <is>
           <t>4a9ec70bde1620a4856a</t>
         </is>
       </c>
-      <c r="K30" t="n">
+      <c r="K29" t="n">
         <v>20</v>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t>skill:Python, skill:TypeScript</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>8cabaf1908a499870002</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>f68789d5d8d6dfcb5e62</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
         <is>
           <t>Merkle Science</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>Software Engineer(Intern)- Backend</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>&amp;nbsp;...Republic, DCG, Kenetic, GGV and several others. 
  Responsibilities 
@@ -2588,73 +2517,73 @@
  Work with  Redis  for caching, queues, and...&amp;nbsp;</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>https://jooble.org/desc/3479600901415878407?ckey=Python+Developer&amp;rgn=55126&amp;pos=5&amp;groupId=40830&amp;elckey=-8489441105830182890&amp;p=1&amp;aq=7420785423372502193&amp;cid=18943&amp;jobAge=658&amp;brelb=15&amp;bscr=52.072277&amp;scr=52.072277</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>https://jooble.org/desc/3479600901415878407?ckey=Python+Developer&amp;rgn=55126&amp;pos=5&amp;groupId=40830&amp;elckey=5755552888213791726&amp;p=1&amp;aq=-3883215854646545784&amp;cid=18943&amp;jobAge=668&amp;brelb=15&amp;bscr=52.409454&amp;scr=52.409454</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
         <is>
           <t>jooble</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>2026-09-03 16:33:17</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>2026-09-03 16:33:17</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>2026-09-04 02:30:49</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2026-09-04 02:30:49</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
         <is>
           <t>c88e76ee05d5f22f3af4</t>
         </is>
       </c>
-      <c r="K31" t="n">
+      <c r="K30" t="n">
         <v>20</v>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="L30" t="inlineStr">
         <is>
           <t>skill:Python, skill:REST APIs</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>a5a97d044631a5032a2d</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>9aaae5112f88cba047d6</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
         <is>
           <t>Merkle Science</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>Software Engineer(Intern)- Backend</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>&amp;nbsp;...several others. 
  Responsibilities 
@@ -2664,73 +2593,73 @@
  Write clean, tested, well-d</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>https://jooble.org/desc/3479600901415878407?ckey=Backend+Engineer&amp;rgn=55126&amp;pos=8&amp;groupId=41745&amp;elckey=-3285534042292215138&amp;p=1&amp;aq=531656242354017487&amp;cid=18943&amp;jobAge=658&amp;brelb=15&amp;bscr=56.879696&amp;scr=56.879696</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>https://jooble.org/away/3479600901415878407?p=1&amp;pos=8&amp;rgn=55126&amp;cid=18943&amp;ckey=Backend+Engineer&amp;jobAge=668&amp;brelb=15&amp;scr=57.15673&amp;bscr=57.15673&amp;aq=8944072254110545486&amp;elckey=-7487284121957792138</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
         <is>
           <t>jooble</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>2026-09-03 16:33:17</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>2026-09-03 16:33:17</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>2026-09-04 02:30:49</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2026-09-04 02:30:49</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
         <is>
           <t>68457383d022598649bc</t>
         </is>
       </c>
-      <c r="K32" t="n">
+      <c r="K31" t="n">
         <v>20</v>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="L31" t="inlineStr">
         <is>
           <t>skill:Python, skill:REST APIs</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>4abbad2faf49987f7f7d</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>a57e0470ca6a0eb97430</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
         <is>
           <t>Mastercard</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>AI Engineer</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>&amp;nbsp;...governments realize their greatest potential.  Title and Summary  AI &lt;b&gt;Engineer &lt;/b&gt;
  Job Description Summary 
@@ -2738,50 +2667,50 @@
 • Develop and maintain scalable AI/ML pipel</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>https://jooble.org/away/6422411571202760777?p=1&amp;pos=17&amp;rgn=55126&amp;cid=18943&amp;ckey=Cloud+Platform+Engineer&amp;jobAge=706&amp;brelb=15&amp;scr=68.48433&amp;bscr=68.48433&amp;aq=-8505660715143753827&amp;elckey=191594000619834446</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>https://jooble.org/desc/6422411571202760777?ckey=Cloud+Platform+Engineer&amp;rgn=55126&amp;pos=17&amp;groupId=1228184036&amp;elckey=-4010156079045742554&amp;p=1&amp;aq=8224623662785434402&amp;cid=18943&amp;jobAge=716&amp;brelb=15&amp;bscr=69.376305&amp;scr=69.376305</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
         <is>
           <t>jooble</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>2026-09-03 16:33:17</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>2026-09-03 16:33:17</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>2026-09-04 02:30:49</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2026-09-04 02:30:49</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
         <is>
           <t>d7e4d97c44e4a78fe1a5</t>
         </is>
       </c>
-      <c r="K33" t="n">
+      <c r="K32" t="n">
         <v>20</v>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="L32" t="inlineStr">
         <is>
           <t>skill:RAG, skill:Agentic AI</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/vignesh_jobs.xlsx
+++ b/data/vignesh_jobs.xlsx
@@ -536,7 +536,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-09-04 02:30:49</t>
+          <t>2026-09-04 04:41:16</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -607,7 +607,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-09-04 02:30:49</t>
+          <t>2026-09-04 04:41:16</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-09-04 02:30:49</t>
+          <t>2026-09-04 04:41:16</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -749,7 +749,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-09-04 02:30:49</t>
+          <t>2026-09-04 04:41:16</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-09-04 02:30:49</t>
+          <t>2026-09-04 04:41:16</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-09-04 02:30:49</t>
+          <t>2026-09-04 04:41:16</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-09-04 02:30:49</t>
+          <t>2026-09-04 04:41:16</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-09-04 02:30:49</t>
+          <t>2026-09-04 04:41:16</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-09-04 02:30:49</t>
+          <t>2026-09-04 04:41:16</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-09-04 02:30:49</t>
+          <t>2026-09-04 04:41:16</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026-09-04 02:30:49</t>
+          <t>2026-09-04 04:41:16</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026-09-04 02:30:49</t>
+          <t>2026-09-04 04:41:16</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2026-09-04 02:30:49</t>
+          <t>2026-09-04 04:41:16</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2026-09-04 02:30:49</t>
+          <t>2026-09-04 04:41:16</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2026-09-04 02:30:49</t>
+          <t>2026-09-04 04:41:16</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2026-09-04 02:30:49</t>
+          <t>2026-09-04 04:41:16</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2026-09-04 02:30:49</t>
+          <t>2026-09-04 04:41:16</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1743,7 +1743,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2026-09-04 02:30:49</t>
+          <t>2026-09-04 04:41:16</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2026-09-04 02:30:49</t>
+          <t>2026-09-04 04:41:16</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1885,7 +1885,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2026-09-04 02:30:49</t>
+          <t>2026-09-04 04:41:16</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2026-09-04 02:30:49</t>
+          <t>2026-09-04 04:41:16</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2027,7 +2027,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2026-09-04 02:30:49</t>
+          <t>2026-09-04 04:41:16</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2098,7 +2098,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2026-09-04 02:30:49</t>
+          <t>2026-09-04 04:41:16</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2169,7 +2169,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2026-09-04 02:30:49</t>
+          <t>2026-09-04 04:41:16</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2240,7 +2240,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2026-09-04 02:30:49</t>
+          <t>2026-09-04 04:41:16</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2311,7 +2311,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2026-09-04 02:30:49</t>
+          <t>2026-09-04 04:41:16</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2342,7 +2342,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>37ef472e64ecfe6212ab</t>
+          <t>45a6a85c287690dc3eb5</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2370,7 +2370,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://jooble.org/desc/6422411571202760777?ckey=AI+Platform+Engineer&amp;rgn=55126&amp;pos=3&amp;groupId=1793437986&amp;elckey=-2964459282113035987&amp;p=1&amp;aq=185338811351190800&amp;cid=18943&amp;jobAge=716&amp;brelb=15&amp;bscr=117.89957&amp;scr=117.89957</t>
+          <t>https://jooble.org/desc/6422411571202760777?ckey=AI+Platform+Engineer&amp;rgn=55126&amp;pos=6&amp;groupId=1793437986&amp;elckey=-6942762892569196287&amp;p=1&amp;aq=-7246069198262714143&amp;cid=18943&amp;jobAge=718&amp;brelb=15&amp;bscr=119.24743&amp;scr=119.24743</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2380,12 +2380,12 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-09-04 02:30:49</t>
+          <t>2026-09-04 04:41:16</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2026-09-04 02:30:49</t>
+          <t>2026-09-04 04:41:16</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2416,7 +2416,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>3ea7622d2452055687f8</t>
+          <t>7b8555b9343b736fc48e</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://jooble.org/away/-4293671604513188386?p=1&amp;pos=3&amp;rgn=55126&amp;cid=18943&amp;ckey=Python+Developer&amp;jobAge=572&amp;brelb=15&amp;scr=52.713013&amp;bscr=52.713013&amp;aq=-3883215854646545784&amp;elckey=5755552888213791726</t>
+          <t>https://jooble.org/desc/-4293671604513188386?ckey=Python+Developer&amp;rgn=55126&amp;pos=2&amp;groupId=40830&amp;elckey=1777249277757631426&amp;p=1&amp;aq=-7765779889963540156&amp;cid=18943&amp;jobAge=574&amp;brelb=15&amp;bscr=54.038685&amp;scr=54.038685</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2454,12 +2454,12 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-09-04 02:30:49</t>
+          <t>2026-09-04 04:41:16</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2026-09-04 02:30:49</t>
+          <t>2026-09-04 04:41:16</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2490,7 +2490,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>f68789d5d8d6dfcb5e62</t>
+          <t>49507e03b9d6dd8fab77</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2519,7 +2519,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://jooble.org/desc/3479600901415878407?ckey=Python+Developer&amp;rgn=55126&amp;pos=5&amp;groupId=40830&amp;elckey=5755552888213791726&amp;p=1&amp;aq=-3883215854646545784&amp;cid=18943&amp;jobAge=668&amp;brelb=15&amp;bscr=52.409454&amp;scr=52.409454</t>
+          <t>https://jooble.org/desc/3479600901415878407?ckey=Python+Developer&amp;rgn=55126&amp;pos=6&amp;groupId=40830&amp;elckey=1777249277757631426&amp;p=1&amp;aq=-7765779889963540156&amp;cid=18943&amp;jobAge=670&amp;brelb=15&amp;bscr=53.364857&amp;scr=53.364857</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2529,12 +2529,12 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-09-04 02:30:49</t>
+          <t>2026-09-04 04:41:16</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2026-09-04 02:30:49</t>
+          <t>2026-09-04 04:41:16</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>9aaae5112f88cba047d6</t>
+          <t>f38e80a94c62e60ae91a</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2595,7 +2595,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://jooble.org/away/3479600901415878407?p=1&amp;pos=8&amp;rgn=55126&amp;cid=18943&amp;ckey=Backend+Engineer&amp;jobAge=668&amp;brelb=15&amp;scr=57.15673&amp;bscr=57.15673&amp;aq=8944072254110545486&amp;elckey=-7487284121957792138</t>
+          <t>https://jooble.org/away/3479600901415878407?p=1&amp;pos=9&amp;rgn=55126&amp;cid=18943&amp;ckey=Backend+Engineer&amp;jobAge=670&amp;brelb=15&amp;scr=57.998188&amp;bscr=57.998188&amp;aq=-4516953858111322769&amp;elckey=6981156341295599178</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2605,12 +2605,12 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-09-04 02:30:49</t>
+          <t>2026-09-04 04:41:16</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2026-09-04 02:30:49</t>
+          <t>2026-09-04 04:41:16</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2641,7 +2641,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>a57e0470ca6a0eb97430</t>
+          <t>b308c354d0a2da138772</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2669,7 +2669,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://jooble.org/desc/6422411571202760777?ckey=Cloud+Platform+Engineer&amp;rgn=55126&amp;pos=17&amp;groupId=1228184036&amp;elckey=-4010156079045742554&amp;p=1&amp;aq=8224623662785434402&amp;cid=18943&amp;jobAge=716&amp;brelb=15&amp;bscr=69.376305&amp;scr=69.376305</t>
+          <t>https://jooble.org/desc/6422411571202760777?ckey=Cloud+Platform+Engineer&amp;rgn=55126&amp;pos=16&amp;groupId=1228184036&amp;elckey=-7988459689501902854&amp;p=1&amp;aq=-6499060195182549996&amp;cid=18943&amp;jobAge=718&amp;brelb=15&amp;bscr=70.468185&amp;scr=70.468185</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2679,12 +2679,12 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-09-04 02:30:49</t>
+          <t>2026-09-04 04:41:16</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2026-09-04 02:30:49</t>
+          <t>2026-09-04 04:41:16</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">

--- a/data/vignesh_jobs.xlsx
+++ b/data/vignesh_jobs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O1"/>
+  <dimension ref="A1:O3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -492,6 +492,145 @@
           <t>Notes</t>
         </is>
       </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>a8cbf0a42f4eb6a851e5</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>C5i</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Job Summary: We’re seeking a highly skilled Full Stack Developer with strong expertise in Python and React, complemented by modern frameworks and cloud-native technologies. The ideal candidate will design and implement scalable, secure, and high-performance applications, integrating front-end and ba</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/land/ad/5876028989?se=9tDroC6t8RGmbN0M_CnU8w&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=2AB1C004D4F1428BA34E00C251D652D0E3EDC43E</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2026-09-10 15:46:37</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2026-09-10 15:46:37</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>2e6e42107f570c2e3e28</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>30</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>skill:Python, skill:Flask, skill:Cloud-Native</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>b089a3cfab02f278c172</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>capco</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>QA Automation Engineer</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>&amp;lt;h3&amp;gt;Shape the Future of Financial Services with Capco&amp;lt;/h3&amp;gt;
+&amp;lt;p&amp;gt;At Capco, we specialize in management consulting and software development, partnering with leading international banks and insurance companies across Western Europe. Our innovative approach and collaborative culture make</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/capco/qa-automation-engineer-118845</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2026-09-10 15:46:37</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2026-09-10 15:46:37</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>b170f1c2eea6a07ed122</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>30</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>skill:REST APIs, skill:SQL, skill:Git</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/vignesh_jobs.xlsx
+++ b/data/vignesh_jobs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O3"/>
+  <dimension ref="A1:O1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -492,145 +492,6 @@
           <t>Notes</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>a8cbf0a42f4eb6a851e5</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>C5i</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Full Stack Engineer</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Bangalore, Karnataka</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Job Summary: We’re seeking a highly skilled Full Stack Developer with strong expertise in Python and React, complemented by modern frameworks and cloud-native technologies. The ideal candidate will design and implement scalable, secure, and high-performance applications, integrating front-end and ba</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>https://www.adzuna.in/land/ad/5876028989?se=9tDroC6t8RGmbN0M_CnU8w&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=2AB1C004D4F1428BA34E00C251D652D0E3EDC43E</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>adzuna</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>2026-09-10 15:46:37</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2026-09-10 15:46:37</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>2e6e42107f570c2e3e28</t>
-        </is>
-      </c>
-      <c r="K2" t="n">
-        <v>30</v>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>skill:Python, skill:Flask, skill:Cloud-Native</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>b089a3cfab02f278c172</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>capco</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>QA Automation Engineer</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>&amp;lt;h3&amp;gt;Shape the Future of Financial Services with Capco&amp;lt;/h3&amp;gt;
-&amp;lt;p&amp;gt;At Capco, we specialize in management consulting and software development, partnering with leading international banks and insurance companies across Western Europe. Our innovative approach and collaborative culture make</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>https://www.arbeitnow.com/jobs/companies/capco/qa-automation-engineer-118845</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>arbeitnow</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>2026-09-10 15:46:37</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2026-09-10 15:46:37</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>b170f1c2eea6a07ed122</t>
-        </is>
-      </c>
-      <c r="K3" t="n">
-        <v>30</v>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>skill:REST APIs, skill:SQL, skill:Git</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
